--- a/winners.xlsx
+++ b/winners.xlsx
@@ -24,31 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
-  <si>
-    <t>farroukh</t>
-  </si>
-  <si>
-    <t>vi</t>
-  </si>
-  <si>
-    <t>nadim</t>
-  </si>
-  <si>
-    <t>mohit</t>
-  </si>
-  <si>
-    <t>vii</t>
-  </si>
-  <si>
-    <t>manoj</t>
-  </si>
-  <si>
-    <t>yogesh</t>
-  </si>
-  <si>
-    <t>ix</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
   <si>
     <t>Admission_Number</t>
   </si>
@@ -57,13 +33,130 @@
   </si>
   <si>
     <t>Class</t>
+  </si>
+  <si>
+    <t>RASHI</t>
+  </si>
+  <si>
+    <t>ANANYA</t>
+  </si>
+  <si>
+    <t>KANIKA</t>
+  </si>
+  <si>
+    <t>VRINDA RANA</t>
+  </si>
+  <si>
+    <t>MYRA</t>
+  </si>
+  <si>
+    <t>SHAURYA</t>
+  </si>
+  <si>
+    <t>ANGAD MANN</t>
+  </si>
+  <si>
+    <t>NUR</t>
+  </si>
+  <si>
+    <t>SUSHANT</t>
+  </si>
+  <si>
+    <t>NILESH KUMAR</t>
+  </si>
+  <si>
+    <t>GAURAV KUMAR</t>
+  </si>
+  <si>
+    <t>DHRUV SHARMA</t>
+  </si>
+  <si>
+    <t>NAMAN</t>
+  </si>
+  <si>
+    <t>ANSHUMAN ROHILLA</t>
+  </si>
+  <si>
+    <t>HANSIKA</t>
+  </si>
+  <si>
+    <t>CHETAN KUMAR</t>
+  </si>
+  <si>
+    <t>TAVISHA</t>
+  </si>
+  <si>
+    <t>UTKARSH VASHISTH</t>
+  </si>
+  <si>
+    <t>HARSH</t>
+  </si>
+  <si>
+    <t>NAVNEET CHAUHAN</t>
+  </si>
+  <si>
+    <t>DOLLY</t>
+  </si>
+  <si>
+    <t>ISHITA JAIN</t>
+  </si>
+  <si>
+    <t>DAKSH</t>
+  </si>
+  <si>
+    <t>VARNIKA DAHIYA</t>
+  </si>
+  <si>
+    <t>HARSHINDER SINGH</t>
+  </si>
+  <si>
+    <t>KRISHNA</t>
+  </si>
+  <si>
+    <t>PRANJAS SINGH</t>
+  </si>
+  <si>
+    <t>VANSHI SINGH</t>
+  </si>
+  <si>
+    <t>VANSH</t>
+  </si>
+  <si>
+    <t>NAINA SAXENA</t>
+  </si>
+  <si>
+    <t>AARUSH MISHRA</t>
+  </si>
+  <si>
+    <t>SHAURYA VERMA</t>
+  </si>
+  <si>
+    <t>PRACHI MANN</t>
+  </si>
+  <si>
+    <t>ANSHIKA MANN</t>
+  </si>
+  <si>
+    <t>MEHAK</t>
+  </si>
+  <si>
+    <t>XII</t>
+  </si>
+  <si>
+    <t>IX</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>XI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,8 +165,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="13.5"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -85,7 +209,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -93,13 +217,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,78 +533,513 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>7351</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>5358</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>5159</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>6222</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5200</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6609</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>9373</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>5222</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>5212</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>6934</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>6019</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>8473</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>5288</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>5255</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>5880</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>5990</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>8275</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>6292</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>7840</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>9027</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>5205</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>8410</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>6743</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>5954</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>6226</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>7032</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>5285</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>5323</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>7354</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>6355</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>5956</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>9417</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>8066</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>5789</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>5302</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/winners.xlsx
+++ b/winners.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="637">
   <si>
     <t>Admission_Number</t>
   </si>
@@ -1932,6 +1932,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>KRITI</t>
   </si>
 </sst>
 </file>
@@ -2202,7 +2205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2387,6 +2390,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10109,7 +10115,15 @@
       </c>
     </row>
     <row r="667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C667" s="54"/>
+      <c r="A667" s="70">
+        <v>6726</v>
+      </c>
+      <c r="B667" s="68" t="s">
+        <v>636</v>
+      </c>
+      <c r="C667" s="69" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="668" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C668" s="54"/>

--- a/winners.xlsx
+++ b/winners.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="702">
   <si>
     <t>Admission_Number</t>
   </si>
@@ -1935,6 +1935,201 @@
   </si>
   <si>
     <t>KRITI</t>
+  </si>
+  <si>
+    <t>VIHAAN KAUSHIK</t>
+  </si>
+  <si>
+    <t>KARTIK VERMA</t>
+  </si>
+  <si>
+    <t>AMRIT KUMAR MISHRA</t>
+  </si>
+  <si>
+    <t>ADVIK SHARMA</t>
+  </si>
+  <si>
+    <t>YANSH SHARMA</t>
+  </si>
+  <si>
+    <t>DHRUV JOSHI</t>
+  </si>
+  <si>
+    <t>KAVISH THAKUR</t>
+  </si>
+  <si>
+    <t>VIRAT KUMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AARAV JAIN </t>
+  </si>
+  <si>
+    <t>AVI</t>
+  </si>
+  <si>
+    <t>ANSH KAUSHIK</t>
+  </si>
+  <si>
+    <t>JAYANT SINGH</t>
+  </si>
+  <si>
+    <t>KRISHNA SHARMA</t>
+  </si>
+  <si>
+    <t>KANISHK</t>
+  </si>
+  <si>
+    <t>AKSH</t>
+  </si>
+  <si>
+    <t>VIHAAN RANA</t>
+  </si>
+  <si>
+    <t>MAYANK RANA</t>
+  </si>
+  <si>
+    <t>YUVRAJ BHARDWAJ</t>
+  </si>
+  <si>
+    <t>ANVI DHIMAN</t>
+  </si>
+  <si>
+    <t>AKANKSHI</t>
+  </si>
+  <si>
+    <t>JEEVIKA</t>
+  </si>
+  <si>
+    <t>CHIRAG KAUSHIK</t>
+  </si>
+  <si>
+    <t>GARVIT GUPTA</t>
+  </si>
+  <si>
+    <t>HIREN</t>
+  </si>
+  <si>
+    <t>KHUSHAAL BALAYAN</t>
+  </si>
+  <si>
+    <t>SURYANSH</t>
+  </si>
+  <si>
+    <t>MAYANK KAUSHIK</t>
+  </si>
+  <si>
+    <t>VIVAAN KHATRI</t>
+  </si>
+  <si>
+    <t>HIMANK MANN</t>
+  </si>
+  <si>
+    <t>DARSH VASHISTH</t>
+  </si>
+  <si>
+    <t>RIYA SHARMA</t>
+  </si>
+  <si>
+    <t>DWIJA PANDEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIHAAN </t>
+  </si>
+  <si>
+    <t>AKSHAT MAAN</t>
+  </si>
+  <si>
+    <t>DEVANK ATRI</t>
+  </si>
+  <si>
+    <t>MASOOM SHARMA</t>
+  </si>
+  <si>
+    <t>SANCHI</t>
+  </si>
+  <si>
+    <t>AAROHI</t>
+  </si>
+  <si>
+    <t>ADITYA KUMAR</t>
+  </si>
+  <si>
+    <t>KUSHAL JOT SINGH</t>
+  </si>
+  <si>
+    <t>RAGHAV GARG</t>
+  </si>
+  <si>
+    <t>AAYUSH CHAUHAN</t>
+  </si>
+  <si>
+    <t>PRATEEK</t>
+  </si>
+  <si>
+    <t>SANKESH</t>
+  </si>
+  <si>
+    <t>TANIKA MALIK</t>
+  </si>
+  <si>
+    <t>ASHUTOSH PATHAK</t>
+  </si>
+  <si>
+    <t>UTKARSH SEHRAWAT</t>
+  </si>
+  <si>
+    <t>CHIRAG RANA</t>
+  </si>
+  <si>
+    <t>PRATEEK SAINI</t>
+  </si>
+  <si>
+    <t>SAMAR KUMAR RANA</t>
+  </si>
+  <si>
+    <t>MANAN GOYAL</t>
+  </si>
+  <si>
+    <t>DIVEN RANA</t>
+  </si>
+  <si>
+    <t>MAYANK SHARMA</t>
+  </si>
+  <si>
+    <t>PRINCE YADAV</t>
+  </si>
+  <si>
+    <t>RAJAT SAHANI</t>
+  </si>
+  <si>
+    <t>ASMIT BALAYAN</t>
+  </si>
+  <si>
+    <t>RUDRA PRATAP SINGH</t>
+  </si>
+  <si>
+    <t>VEER CHAUHAN</t>
+  </si>
+  <si>
+    <t>RACHIT CHAUHAN</t>
+  </si>
+  <si>
+    <t>RISHABH KUMAR</t>
+  </si>
+  <si>
+    <t>ISHAN KUMAR</t>
+  </si>
+  <si>
+    <t>DAKSH GOEL</t>
+  </si>
+  <si>
+    <t>DEVANSH GARG</t>
+  </si>
+  <si>
+    <t>BHUMI CHAUHAN</t>
+  </si>
+  <si>
+    <t>ASHIKA GOEL</t>
   </si>
 </sst>
 </file>
@@ -10126,259 +10321,939 @@
       </c>
     </row>
     <row r="668" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C668" s="54"/>
+      <c r="A668" s="57">
+        <v>8807</v>
+      </c>
+      <c r="B668" s="57" t="s">
+        <v>637</v>
+      </c>
+      <c r="C668" s="6" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C669" s="54"/>
+      <c r="A669" s="57">
+        <v>8830</v>
+      </c>
+      <c r="B669" s="57" t="s">
+        <v>638</v>
+      </c>
+      <c r="C669" s="6" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C670" s="54"/>
+      <c r="A670" s="57">
+        <v>8467</v>
+      </c>
+      <c r="B670" s="57" t="s">
+        <v>639</v>
+      </c>
+      <c r="C670" s="6" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C671" s="54"/>
+      <c r="A671" s="57">
+        <v>9482</v>
+      </c>
+      <c r="B671" s="57" t="s">
+        <v>640</v>
+      </c>
+      <c r="C671" s="6" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C672" s="54"/>
-    </row>
-    <row r="673" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C673" s="54"/>
-    </row>
-    <row r="674" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C674" s="54"/>
-    </row>
-    <row r="675" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C675" s="54"/>
-    </row>
-    <row r="676" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C676" s="54"/>
-    </row>
-    <row r="677" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C677" s="54"/>
-    </row>
-    <row r="678" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C678" s="54"/>
-    </row>
-    <row r="679" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C679" s="54"/>
-    </row>
-    <row r="680" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C680" s="54"/>
-    </row>
-    <row r="681" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C681" s="54"/>
-    </row>
-    <row r="682" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C682" s="54"/>
-    </row>
-    <row r="683" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C683" s="54"/>
-    </row>
-    <row r="684" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C684" s="54"/>
-    </row>
-    <row r="685" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C685" s="54"/>
-    </row>
-    <row r="686" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C686" s="54"/>
-    </row>
-    <row r="687" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C687" s="54"/>
-    </row>
-    <row r="688" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C688" s="54"/>
-    </row>
-    <row r="689" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C689" s="54"/>
-    </row>
-    <row r="690" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C690" s="54"/>
-    </row>
-    <row r="691" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C691" s="54"/>
-    </row>
-    <row r="692" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C692" s="54"/>
-    </row>
-    <row r="693" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C693" s="54"/>
-    </row>
-    <row r="694" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C694" s="54"/>
-    </row>
-    <row r="695" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C695" s="54"/>
-    </row>
-    <row r="696" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C696" s="54"/>
-    </row>
-    <row r="697" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C697" s="54"/>
-    </row>
-    <row r="698" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C698" s="54"/>
-    </row>
-    <row r="699" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C699" s="54"/>
-    </row>
-    <row r="700" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C700" s="54"/>
-    </row>
-    <row r="701" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C701" s="54"/>
-    </row>
-    <row r="702" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C702" s="54"/>
-    </row>
-    <row r="703" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C703" s="54"/>
-    </row>
-    <row r="704" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C704" s="54"/>
-    </row>
-    <row r="705" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C705" s="54"/>
-    </row>
-    <row r="706" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C706" s="54"/>
-    </row>
-    <row r="707" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C707" s="54"/>
-    </row>
-    <row r="708" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C708" s="54"/>
-    </row>
-    <row r="709" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C709" s="54"/>
-    </row>
-    <row r="710" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C710" s="54"/>
-    </row>
-    <row r="711" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C711" s="54"/>
-    </row>
-    <row r="712" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C712" s="54"/>
-    </row>
-    <row r="713" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C713" s="54"/>
-    </row>
-    <row r="714" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C714" s="54"/>
-    </row>
-    <row r="715" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C715" s="54"/>
-    </row>
-    <row r="716" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C716" s="54"/>
-    </row>
-    <row r="717" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C717" s="54"/>
-    </row>
-    <row r="718" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C718" s="54"/>
-    </row>
-    <row r="719" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C719" s="54"/>
-    </row>
-    <row r="720" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C720" s="54"/>
-    </row>
-    <row r="721" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C721" s="54"/>
-    </row>
-    <row r="722" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C722" s="54"/>
-    </row>
-    <row r="723" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C723" s="54"/>
-    </row>
-    <row r="724" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C724" s="54"/>
-    </row>
-    <row r="725" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C725" s="54"/>
-    </row>
-    <row r="726" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C726" s="54"/>
-    </row>
-    <row r="727" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C727" s="54"/>
-    </row>
-    <row r="728" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C728" s="54"/>
-    </row>
-    <row r="729" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C729" s="54"/>
-    </row>
-    <row r="730" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C730" s="54"/>
-    </row>
-    <row r="731" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C731" s="54"/>
-    </row>
-    <row r="732" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C732" s="54"/>
-    </row>
-    <row r="733" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C733" s="54"/>
-    </row>
-    <row r="734" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C734" s="54"/>
-    </row>
-    <row r="735" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C735" s="54"/>
-    </row>
-    <row r="736" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C736" s="54"/>
-    </row>
-    <row r="737" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C737" s="54"/>
-    </row>
-    <row r="738" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C738" s="54"/>
-    </row>
-    <row r="739" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C739" s="54"/>
-    </row>
-    <row r="740" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C740" s="54"/>
-    </row>
-    <row r="741" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C741" s="54"/>
-    </row>
-    <row r="742" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C742" s="54"/>
-    </row>
-    <row r="743" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C743" s="54"/>
-    </row>
-    <row r="744" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C744" s="54"/>
-    </row>
-    <row r="745" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C745" s="54"/>
-    </row>
-    <row r="746" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C746" s="54"/>
-    </row>
-    <row r="747" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C747" s="54"/>
-    </row>
-    <row r="748" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C748" s="54"/>
-    </row>
-    <row r="749" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C749" s="54"/>
-    </row>
-    <row r="750" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C750" s="54"/>
-    </row>
-    <row r="751" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C751" s="54"/>
-    </row>
-    <row r="752" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C752" s="54"/>
+      <c r="A672" s="57">
+        <v>8908</v>
+      </c>
+      <c r="B672" s="57" t="s">
+        <v>641</v>
+      </c>
+      <c r="C672" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A673" s="57">
+        <v>7231</v>
+      </c>
+      <c r="B673" s="57" t="s">
+        <v>642</v>
+      </c>
+      <c r="C673" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A674" s="57">
+        <v>8224</v>
+      </c>
+      <c r="B674" s="57" t="s">
+        <v>643</v>
+      </c>
+      <c r="C674" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A675" s="57">
+        <v>8204</v>
+      </c>
+      <c r="B675" s="57" t="s">
+        <v>644</v>
+      </c>
+      <c r="C675" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A676" s="57">
+        <v>8131</v>
+      </c>
+      <c r="B676" s="57" t="s">
+        <v>645</v>
+      </c>
+      <c r="C676" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A677" s="57">
+        <v>8855</v>
+      </c>
+      <c r="B677" s="57" t="s">
+        <v>646</v>
+      </c>
+      <c r="C677" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A678" s="57">
+        <v>9439</v>
+      </c>
+      <c r="B678" s="57" t="s">
+        <v>647</v>
+      </c>
+      <c r="C678" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A679" s="57">
+        <v>6601</v>
+      </c>
+      <c r="B679" s="57" t="s">
+        <v>648</v>
+      </c>
+      <c r="C679" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A680" s="57">
+        <v>7965</v>
+      </c>
+      <c r="B680" s="57" t="s">
+        <v>649</v>
+      </c>
+      <c r="C680" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A681" s="57">
+        <v>7716</v>
+      </c>
+      <c r="B681" s="57" t="s">
+        <v>650</v>
+      </c>
+      <c r="C681" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A682" s="57">
+        <v>9413</v>
+      </c>
+      <c r="B682" s="57" t="s">
+        <v>651</v>
+      </c>
+      <c r="C682" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A683" s="57">
+        <v>6395</v>
+      </c>
+      <c r="B683" s="57" t="s">
+        <v>652</v>
+      </c>
+      <c r="C683" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A684" s="57">
+        <v>6542</v>
+      </c>
+      <c r="B684" s="57" t="s">
+        <v>653</v>
+      </c>
+      <c r="C684" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A685" s="57">
+        <v>9151</v>
+      </c>
+      <c r="B685" s="57" t="s">
+        <v>654</v>
+      </c>
+      <c r="C685" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A686" s="57">
+        <v>6479</v>
+      </c>
+      <c r="B686" s="57" t="s">
+        <v>655</v>
+      </c>
+      <c r="C686" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A687" s="57">
+        <v>7925</v>
+      </c>
+      <c r="B687" s="57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C687" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A688" s="57">
+        <v>6510</v>
+      </c>
+      <c r="B688" s="57" t="s">
+        <v>656</v>
+      </c>
+      <c r="C688" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A689" s="57">
+        <v>6420</v>
+      </c>
+      <c r="B689" s="57" t="s">
+        <v>657</v>
+      </c>
+      <c r="C689" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A690" s="57">
+        <v>6442</v>
+      </c>
+      <c r="B690" s="57" t="s">
+        <v>658</v>
+      </c>
+      <c r="C690" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A691" s="57">
+        <v>6423</v>
+      </c>
+      <c r="B691" s="57" t="s">
+        <v>659</v>
+      </c>
+      <c r="C691" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A692" s="57">
+        <v>9477</v>
+      </c>
+      <c r="B692" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C692" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A693" s="57">
+        <v>7442</v>
+      </c>
+      <c r="B693" s="57" t="s">
+        <v>661</v>
+      </c>
+      <c r="C693" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A694" s="57">
+        <v>8443</v>
+      </c>
+      <c r="B694" s="57" t="s">
+        <v>662</v>
+      </c>
+      <c r="C694" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A695" s="57">
+        <v>7193</v>
+      </c>
+      <c r="B695" s="57" t="s">
+        <v>663</v>
+      </c>
+      <c r="C695" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A696" s="57">
+        <v>6749</v>
+      </c>
+      <c r="B696" s="57" t="s">
+        <v>652</v>
+      </c>
+      <c r="C696" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A697" s="57">
+        <v>6406</v>
+      </c>
+      <c r="B697" s="57" t="s">
+        <v>664</v>
+      </c>
+      <c r="C697" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A698" s="57">
+        <v>6379</v>
+      </c>
+      <c r="B698" s="57" t="s">
+        <v>665</v>
+      </c>
+      <c r="C698" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A699" s="57">
+        <v>8274</v>
+      </c>
+      <c r="B699" s="57" t="s">
+        <v>666</v>
+      </c>
+      <c r="C699" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A700" s="57">
+        <v>7532</v>
+      </c>
+      <c r="B700" s="57" t="s">
+        <v>667</v>
+      </c>
+      <c r="C700" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A701" s="57">
+        <v>8047</v>
+      </c>
+      <c r="B701" s="57" t="s">
+        <v>668</v>
+      </c>
+      <c r="C701" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A702" s="57">
+        <v>7700</v>
+      </c>
+      <c r="B702" s="57" t="s">
+        <v>669</v>
+      </c>
+      <c r="C702" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A703" s="57">
+        <v>9449</v>
+      </c>
+      <c r="B703" s="57" t="s">
+        <v>646</v>
+      </c>
+      <c r="C703" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A704" s="57">
+        <v>6170</v>
+      </c>
+      <c r="B704" s="57" t="s">
+        <v>670</v>
+      </c>
+      <c r="C704" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A705" s="57">
+        <v>6174</v>
+      </c>
+      <c r="B705" s="57" t="s">
+        <v>671</v>
+      </c>
+      <c r="C705" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A706" s="57">
+        <v>9581</v>
+      </c>
+      <c r="B706" s="57" t="s">
+        <v>672</v>
+      </c>
+      <c r="C706" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A707" s="57">
+        <v>7365</v>
+      </c>
+      <c r="B707" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="C707" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A708" s="57">
+        <v>6875</v>
+      </c>
+      <c r="B708" s="57" t="s">
+        <v>673</v>
+      </c>
+      <c r="C708" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A709" s="57">
+        <v>6463</v>
+      </c>
+      <c r="B709" s="57" t="s">
+        <v>674</v>
+      </c>
+      <c r="C709" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A710" s="57">
+        <v>6145</v>
+      </c>
+      <c r="B710" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C710" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A711" s="57">
+        <v>8102</v>
+      </c>
+      <c r="B711" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="C711" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A712" s="57">
+        <v>6343</v>
+      </c>
+      <c r="B712" s="57" t="s">
+        <v>675</v>
+      </c>
+      <c r="C712" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A713" s="57">
+        <v>7824</v>
+      </c>
+      <c r="B713" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C713" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A714" s="57">
+        <v>6980</v>
+      </c>
+      <c r="B714" s="57" t="s">
+        <v>361</v>
+      </c>
+      <c r="C714" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A715" s="57">
+        <v>5899</v>
+      </c>
+      <c r="B715" s="57" t="s">
+        <v>676</v>
+      </c>
+      <c r="C715" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A716" s="57">
+        <v>8139</v>
+      </c>
+      <c r="B716" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C716" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A717" s="57">
+        <v>6921</v>
+      </c>
+      <c r="B717" s="57" t="s">
+        <v>677</v>
+      </c>
+      <c r="C717" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A718" s="57">
+        <v>8638</v>
+      </c>
+      <c r="B718" s="57" t="s">
+        <v>678</v>
+      </c>
+      <c r="C718" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A719" s="57">
+        <v>6960</v>
+      </c>
+      <c r="B719" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C719" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A720" s="57">
+        <v>5933</v>
+      </c>
+      <c r="B720" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="C720" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A721" s="57">
+        <v>5854</v>
+      </c>
+      <c r="B721" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="C721" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A722" s="57">
+        <v>6401</v>
+      </c>
+      <c r="B722" s="57" t="s">
+        <v>552</v>
+      </c>
+      <c r="C722" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A723" s="57">
+        <v>5913</v>
+      </c>
+      <c r="B723" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C723" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A724" s="57">
+        <v>5850</v>
+      </c>
+      <c r="B724" s="57" t="s">
+        <v>679</v>
+      </c>
+      <c r="C724" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A725" s="57">
+        <v>6484</v>
+      </c>
+      <c r="B725" s="57" t="s">
+        <v>680</v>
+      </c>
+      <c r="C725" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A726" s="57">
+        <v>5866</v>
+      </c>
+      <c r="B726" s="57" t="s">
+        <v>377</v>
+      </c>
+      <c r="C726" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A727" s="57">
+        <v>5841</v>
+      </c>
+      <c r="B727" s="57" t="s">
+        <v>681</v>
+      </c>
+      <c r="C727" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A728" s="57">
+        <v>7962</v>
+      </c>
+      <c r="B728" s="57" t="s">
+        <v>682</v>
+      </c>
+      <c r="C728" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A729" s="57">
+        <v>8918</v>
+      </c>
+      <c r="B729" s="57" t="s">
+        <v>683</v>
+      </c>
+      <c r="C729" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A730" s="57">
+        <v>6572</v>
+      </c>
+      <c r="B730" s="57" t="s">
+        <v>684</v>
+      </c>
+      <c r="C730" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A731" s="57">
+        <v>5857</v>
+      </c>
+      <c r="B731" s="57" t="s">
+        <v>685</v>
+      </c>
+      <c r="C731" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A732" s="57">
+        <v>5849</v>
+      </c>
+      <c r="B732" s="57" t="s">
+        <v>550</v>
+      </c>
+      <c r="C732" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A733" s="57">
+        <v>6789</v>
+      </c>
+      <c r="B733" s="57" t="s">
+        <v>686</v>
+      </c>
+      <c r="C733" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A734" s="57">
+        <v>6925</v>
+      </c>
+      <c r="B734" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C734" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A735" s="57">
+        <v>5902</v>
+      </c>
+      <c r="B735" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C735" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A736" s="57">
+        <v>8824</v>
+      </c>
+      <c r="B736" s="57" t="s">
+        <v>687</v>
+      </c>
+      <c r="C736" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A737" s="57">
+        <v>5898</v>
+      </c>
+      <c r="B737" s="57" t="s">
+        <v>688</v>
+      </c>
+      <c r="C737" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A738" s="57">
+        <v>8826</v>
+      </c>
+      <c r="B738" s="57" t="s">
+        <v>689</v>
+      </c>
+      <c r="C738" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A739" s="57">
+        <v>8478</v>
+      </c>
+      <c r="B739" s="57" t="s">
+        <v>690</v>
+      </c>
+      <c r="C739" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A740" s="57">
+        <v>5937</v>
+      </c>
+      <c r="B740" s="57" t="s">
+        <v>691</v>
+      </c>
+      <c r="C740" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A741" s="57">
+        <v>5916</v>
+      </c>
+      <c r="B741" s="57" t="s">
+        <v>692</v>
+      </c>
+      <c r="C741" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A742" s="57">
+        <v>6806</v>
+      </c>
+      <c r="B742" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="C742" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A743" s="57">
+        <v>5882</v>
+      </c>
+      <c r="B743" s="57" t="s">
+        <v>693</v>
+      </c>
+      <c r="C743" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A744" s="57">
+        <v>5958</v>
+      </c>
+      <c r="B744" s="57" t="s">
+        <v>694</v>
+      </c>
+      <c r="C744" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A745" s="57">
+        <v>9244</v>
+      </c>
+      <c r="B745" s="57" t="s">
+        <v>695</v>
+      </c>
+      <c r="C745" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A746" s="57">
+        <v>6662</v>
+      </c>
+      <c r="B746" s="57" t="s">
+        <v>696</v>
+      </c>
+      <c r="C746" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A747" s="57">
+        <v>8369</v>
+      </c>
+      <c r="B747" s="57" t="s">
+        <v>697</v>
+      </c>
+      <c r="C747" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A748" s="57">
+        <v>5894</v>
+      </c>
+      <c r="B748" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="C748" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A749" s="57">
+        <v>6009</v>
+      </c>
+      <c r="B749" s="57" t="s">
+        <v>698</v>
+      </c>
+      <c r="C749" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A750" s="57">
+        <v>5845</v>
+      </c>
+      <c r="B750" s="57" t="s">
+        <v>699</v>
+      </c>
+      <c r="C750" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A751" s="57">
+        <v>5840</v>
+      </c>
+      <c r="B751" s="57" t="s">
+        <v>700</v>
+      </c>
+      <c r="C751" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A752" s="57">
+        <v>5989</v>
+      </c>
+      <c r="B752" s="57" t="s">
+        <v>701</v>
+      </c>
+      <c r="C752" s="6" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="753" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C753" s="54"/>

--- a/winners.xlsx
+++ b/winners.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="725">
   <si>
     <t>Admission_Number</t>
   </si>
@@ -2130,6 +2130,75 @@
   </si>
   <si>
     <t>ASHIKA GOEL</t>
+  </si>
+  <si>
+    <t>SHOBIT BHARDWAJ</t>
+  </si>
+  <si>
+    <t>HARSH SINGHAL</t>
+  </si>
+  <si>
+    <t>BHAVI</t>
+  </si>
+  <si>
+    <t>HIMANSHI</t>
+  </si>
+  <si>
+    <t>AARNAV MANN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEHUL JAIN </t>
+  </si>
+  <si>
+    <t>ANKUR TYAGI *</t>
+  </si>
+  <si>
+    <t>AAYAN*</t>
+  </si>
+  <si>
+    <t>ANSHUMAN BHARDWAJ</t>
+  </si>
+  <si>
+    <t>EIRIK MANN</t>
+  </si>
+  <si>
+    <t>LAVISH RANA</t>
+  </si>
+  <si>
+    <t>YATHARTH SINGH</t>
+  </si>
+  <si>
+    <t>AYUSH SAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAIBHAV SAINI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VISHNU SHARMA </t>
+  </si>
+  <si>
+    <t>PRATYUSH BANSAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">YASH JOSHI </t>
+  </si>
+  <si>
+    <t>MUKUL</t>
+  </si>
+  <si>
+    <t>CHIRAG GOEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JIYANSHU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIRAJ </t>
+  </si>
+  <si>
+    <t>RISHABH DUHAN</t>
   </si>
 </sst>
 </file>
@@ -2271,7 +2340,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2396,11 +2465,132 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2587,6 +2777,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11212,143 +11448,335 @@
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A749" s="57">
+      <c r="A749" s="73">
         <v>6009</v>
       </c>
-      <c r="B749" s="57" t="s">
+      <c r="B749" s="73" t="s">
         <v>698</v>
       </c>
-      <c r="C749" s="6" t="s">
+      <c r="C749" s="74" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A750" s="57">
+      <c r="A750" s="73">
         <v>5845</v>
       </c>
-      <c r="B750" s="57" t="s">
+      <c r="B750" s="73" t="s">
         <v>699</v>
       </c>
-      <c r="C750" s="6" t="s">
+      <c r="C750" s="74" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A751" s="57">
+      <c r="A751" s="73">
         <v>5840</v>
       </c>
-      <c r="B751" s="57" t="s">
+      <c r="B751" s="73" t="s">
         <v>700</v>
       </c>
-      <c r="C751" s="6" t="s">
+      <c r="C751" s="74" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A752" s="57">
+    <row r="752" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A752" s="73">
         <v>5989</v>
       </c>
-      <c r="B752" s="57" t="s">
+      <c r="B752" s="73" t="s">
         <v>701</v>
       </c>
-      <c r="C752" s="6" t="s">
+      <c r="C752" s="74" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="753" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C753" s="54"/>
-    </row>
-    <row r="754" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C754" s="54"/>
-    </row>
-    <row r="755" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C755" s="54"/>
-    </row>
-    <row r="756" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C756" s="54"/>
-    </row>
-    <row r="757" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C757" s="54"/>
-    </row>
-    <row r="758" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C758" s="54"/>
-    </row>
-    <row r="759" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C759" s="54"/>
-    </row>
-    <row r="760" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C760" s="54"/>
-    </row>
-    <row r="761" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C761" s="54"/>
-    </row>
-    <row r="762" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C762" s="54"/>
-    </row>
-    <row r="763" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C763" s="54"/>
-    </row>
-    <row r="764" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C764" s="54"/>
-    </row>
-    <row r="765" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C765" s="54"/>
-    </row>
-    <row r="766" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C766" s="54"/>
-    </row>
-    <row r="767" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C767" s="54"/>
-    </row>
-    <row r="768" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C768" s="54"/>
-    </row>
-    <row r="769" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C769" s="54"/>
-    </row>
-    <row r="770" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C770" s="54"/>
-    </row>
-    <row r="771" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C771" s="54"/>
-    </row>
-    <row r="772" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C772" s="54"/>
-    </row>
-    <row r="773" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C773" s="54"/>
-    </row>
-    <row r="774" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C774" s="54"/>
-    </row>
-    <row r="775" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C775" s="54"/>
-    </row>
-    <row r="776" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C776" s="54"/>
-    </row>
-    <row r="777" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A753" s="75">
+        <v>5528</v>
+      </c>
+      <c r="B753" s="76" t="s">
+        <v>702</v>
+      </c>
+      <c r="C753" s="76" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A754" s="77">
+        <v>7580</v>
+      </c>
+      <c r="B754" s="78" t="s">
+        <v>703</v>
+      </c>
+      <c r="C754" s="78" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A755" s="79">
+        <v>4867</v>
+      </c>
+      <c r="B755" s="80" t="s">
+        <v>704</v>
+      </c>
+      <c r="C755" s="80" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A756" s="79">
+        <v>7767</v>
+      </c>
+      <c r="B756" s="80" t="s">
+        <v>705</v>
+      </c>
+      <c r="C756" s="80" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A757" s="71">
+        <v>7928</v>
+      </c>
+      <c r="B757" s="72" t="s">
+        <v>520</v>
+      </c>
+      <c r="C757" s="86" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A758" s="81">
+        <v>6187</v>
+      </c>
+      <c r="B758" s="83" t="s">
+        <v>706</v>
+      </c>
+      <c r="C758" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="759" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A759" s="82">
+        <v>6249</v>
+      </c>
+      <c r="B759" s="84" t="s">
+        <v>707</v>
+      </c>
+      <c r="C759" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A760" s="82">
+        <v>6180</v>
+      </c>
+      <c r="B760" s="84" t="s">
+        <v>708</v>
+      </c>
+      <c r="C760" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A761" s="82">
+        <v>6242</v>
+      </c>
+      <c r="B761" s="85" t="s">
+        <v>709</v>
+      </c>
+      <c r="C761" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A762" s="82">
+        <v>6788</v>
+      </c>
+      <c r="B762" s="85" t="s">
+        <v>710</v>
+      </c>
+      <c r="C762" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A763" s="82">
+        <v>8254</v>
+      </c>
+      <c r="B763" s="85" t="s">
+        <v>711</v>
+      </c>
+      <c r="C763" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A764" s="82">
+        <v>8468</v>
+      </c>
+      <c r="B764" s="85" t="s">
+        <v>712</v>
+      </c>
+      <c r="C764" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A765" s="82">
+        <v>8624</v>
+      </c>
+      <c r="B765" s="85" t="s">
+        <v>713</v>
+      </c>
+      <c r="C765" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A766" s="82">
+        <v>7298</v>
+      </c>
+      <c r="B766" s="85" t="s">
+        <v>714</v>
+      </c>
+      <c r="C766" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A767" s="82">
+        <v>6333</v>
+      </c>
+      <c r="B767" s="85" t="s">
+        <v>715</v>
+      </c>
+      <c r="C767" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A768" s="82">
+        <v>8713</v>
+      </c>
+      <c r="B768" s="85" t="s">
+        <v>716</v>
+      </c>
+      <c r="C768" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A769" s="82">
+        <v>8600</v>
+      </c>
+      <c r="B769" s="85" t="s">
+        <v>717</v>
+      </c>
+      <c r="C769" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A770" s="82">
+        <v>9209</v>
+      </c>
+      <c r="B770" s="85" t="s">
+        <v>718</v>
+      </c>
+      <c r="C770" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A771" s="82">
+        <v>6160</v>
+      </c>
+      <c r="B771" s="85" t="s">
+        <v>719</v>
+      </c>
+      <c r="C771" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A772" s="82">
+        <v>6968</v>
+      </c>
+      <c r="B772" s="85" t="s">
+        <v>720</v>
+      </c>
+      <c r="C772" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A773" s="82">
+        <v>8574</v>
+      </c>
+      <c r="B773" s="85" t="s">
+        <v>721</v>
+      </c>
+      <c r="C773" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A774" s="82">
+        <v>6892</v>
+      </c>
+      <c r="B774" s="85" t="s">
+        <v>722</v>
+      </c>
+      <c r="C774" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A775" s="82">
+        <v>8276</v>
+      </c>
+      <c r="B775" s="85" t="s">
+        <v>723</v>
+      </c>
+      <c r="C775" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A776" s="82">
+        <v>9029</v>
+      </c>
+      <c r="B776" s="85" t="s">
+        <v>724</v>
+      </c>
+      <c r="C776" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C777" s="54"/>
     </row>
-    <row r="778" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C778" s="54"/>
     </row>
-    <row r="779" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C779" s="54"/>
     </row>
-    <row r="780" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C780" s="54"/>
     </row>
-    <row r="781" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C781" s="54"/>
     </row>
-    <row r="782" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C782" s="54"/>
     </row>
-    <row r="783" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C783" s="54"/>
     </row>
-    <row r="784" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C784" s="54"/>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.25">

--- a/winners.xlsx
+++ b/winners.xlsx
@@ -6203,7 +6203,9 @@
       </c>
     </row>
     <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A272" s="24"/>
+      <c r="A272" s="24">
+        <v>9525</v>
+      </c>
       <c r="B272" s="45" t="s">
         <v>282</v>
       </c>

--- a/winners.xlsx
+++ b/winners.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="726">
   <si>
     <t>Admission_Number</t>
   </si>
@@ -1859,9 +1859,6 @@
     <t>TANNU YADAV</t>
   </si>
   <si>
-    <t>SAMIKSHA</t>
-  </si>
-  <si>
     <t>AANVIKSHIKI ANAND</t>
   </si>
   <si>
@@ -2150,12 +2147,6 @@
     <t xml:space="preserve">MEHUL JAIN </t>
   </si>
   <si>
-    <t>ANKUR TYAGI *</t>
-  </si>
-  <si>
-    <t>AAYAN*</t>
-  </si>
-  <si>
     <t>ANSHUMAN BHARDWAJ</t>
   </si>
   <si>
@@ -2199,6 +2190,18 @@
   </si>
   <si>
     <t>RISHABH DUHAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANKUR TYAGI </t>
+  </si>
+  <si>
+    <t>AAYAN</t>
+  </si>
+  <si>
+    <t>YUVRAJ YADAV</t>
+  </si>
+  <si>
+    <t>SAMEEKSHA SINGH</t>
   </si>
 </sst>
 </file>
@@ -2320,7 +2323,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2333,14 +2336,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -2586,11 +2583,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2720,9 +2728,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2778,9 +2783,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2788,29 +2790,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2823,6 +2810,42 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3110,7 +3133,7 @@
     <col min="1" max="1" width="7.28515625" style="31" customWidth="1"/>
     <col min="2" max="2" width="34.28515625" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="6"/>
-    <col min="4" max="4" width="9.140625" style="54"/>
+    <col min="4" max="4" width="9.140625" style="53"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
@@ -5873,14 +5896,14 @@
       <c r="A242" s="24">
         <v>9005</v>
       </c>
-      <c r="B242" s="47" t="s">
+      <c r="B242" s="84" t="s">
         <v>223</v>
       </c>
       <c r="C242" s="10" t="s">
         <v>222</v>
       </c>
       <c r="J242" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -6151,7 +6174,7 @@
       <c r="A267" s="26">
         <v>9492</v>
       </c>
-      <c r="B267" s="48" t="s">
+      <c r="B267" s="47" t="s">
         <v>276</v>
       </c>
       <c r="C267" s="10" t="s">
@@ -6195,7 +6218,7 @@
       <c r="A271" s="26">
         <v>8405</v>
       </c>
-      <c r="B271" s="49" t="s">
+      <c r="B271" s="48" t="s">
         <v>280</v>
       </c>
       <c r="C271" s="9" t="s">
@@ -6690,7 +6713,7 @@
       <c r="A316" s="26">
         <v>8564</v>
       </c>
-      <c r="B316" s="49" t="s">
+      <c r="B316" s="48" t="s">
         <v>322</v>
       </c>
       <c r="C316" s="9" t="s">
@@ -7130,7 +7153,7 @@
       <c r="A356" s="27">
         <v>8292</v>
       </c>
-      <c r="B356" s="48" t="s">
+      <c r="B356" s="47" t="s">
         <v>357</v>
       </c>
       <c r="C356" s="10" t="s">
@@ -7548,7 +7571,7 @@
       <c r="A394" s="27">
         <v>8783</v>
       </c>
-      <c r="B394" s="48" t="s">
+      <c r="B394" s="47" t="s">
         <v>393</v>
       </c>
       <c r="C394" s="9" t="s">
@@ -7878,7 +7901,7 @@
       <c r="A424" s="27">
         <v>6879</v>
       </c>
-      <c r="B424" s="48" t="s">
+      <c r="B424" s="47" t="s">
         <v>421</v>
       </c>
       <c r="C424" s="9" t="s">
@@ -8142,7 +8165,7 @@
       <c r="A448" s="26">
         <v>8231</v>
       </c>
-      <c r="B448" s="48" t="s">
+      <c r="B448" s="47" t="s">
         <v>444</v>
       </c>
       <c r="C448" s="9" t="s">
@@ -8406,7 +8429,7 @@
       <c r="A472" s="26">
         <v>8371</v>
       </c>
-      <c r="B472" s="49" t="s">
+      <c r="B472" s="48" t="s">
         <v>467</v>
       </c>
       <c r="C472" s="9" t="s">
@@ -8417,7 +8440,7 @@
       <c r="A473" s="24">
         <v>9135</v>
       </c>
-      <c r="B473" s="50" t="s">
+      <c r="B473" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C473" s="7" t="s">
@@ -8428,7 +8451,7 @@
       <c r="A474" s="24">
         <v>9565</v>
       </c>
-      <c r="B474" s="50" t="s">
+      <c r="B474" s="49" t="s">
         <v>469</v>
       </c>
       <c r="C474" s="7" t="s">
@@ -8439,7 +8462,7 @@
       <c r="A475" s="24">
         <v>9425</v>
       </c>
-      <c r="B475" s="50" t="s">
+      <c r="B475" s="49" t="s">
         <v>470</v>
       </c>
       <c r="C475" s="7" t="s">
@@ -8450,7 +8473,7 @@
       <c r="A476" s="24">
         <v>8342</v>
       </c>
-      <c r="B476" s="50" t="s">
+      <c r="B476" s="49" t="s">
         <v>471</v>
       </c>
       <c r="C476" s="7" t="s">
@@ -8461,7 +8484,7 @@
       <c r="A477" s="24">
         <v>8472</v>
       </c>
-      <c r="B477" s="50" t="s">
+      <c r="B477" s="49" t="s">
         <v>472</v>
       </c>
       <c r="C477" s="7" t="s">
@@ -8472,7 +8495,7 @@
       <c r="A478" s="24">
         <v>7903</v>
       </c>
-      <c r="B478" s="50" t="s">
+      <c r="B478" s="49" t="s">
         <v>473</v>
       </c>
       <c r="C478" s="7" t="s">
@@ -8483,7 +8506,7 @@
       <c r="A479" s="24">
         <v>8352</v>
       </c>
-      <c r="B479" s="50" t="s">
+      <c r="B479" s="49" t="s">
         <v>474</v>
       </c>
       <c r="C479" s="7" t="s">
@@ -8494,7 +8517,7 @@
       <c r="A480" s="24">
         <v>8934</v>
       </c>
-      <c r="B480" s="50" t="s">
+      <c r="B480" s="49" t="s">
         <v>475</v>
       </c>
       <c r="C480" s="7" t="s">
@@ -8505,7 +8528,7 @@
       <c r="A481" s="24">
         <v>8202</v>
       </c>
-      <c r="B481" s="50" t="s">
+      <c r="B481" s="49" t="s">
         <v>476</v>
       </c>
       <c r="C481" s="7" t="s">
@@ -8516,7 +8539,7 @@
       <c r="A482" s="24">
         <v>7667</v>
       </c>
-      <c r="B482" s="50" t="s">
+      <c r="B482" s="49" t="s">
         <v>477</v>
       </c>
       <c r="C482" s="7" t="s">
@@ -8527,7 +8550,7 @@
       <c r="A483" s="24">
         <v>8075</v>
       </c>
-      <c r="B483" s="50" t="s">
+      <c r="B483" s="49" t="s">
         <v>478</v>
       </c>
       <c r="C483" s="7" t="s">
@@ -8538,7 +8561,7 @@
       <c r="A484" s="24">
         <v>8046</v>
       </c>
-      <c r="B484" s="50" t="s">
+      <c r="B484" s="49" t="s">
         <v>479</v>
       </c>
       <c r="C484" s="7" t="s">
@@ -8549,7 +8572,7 @@
       <c r="A485" s="24">
         <v>7923</v>
       </c>
-      <c r="B485" s="50" t="s">
+      <c r="B485" s="49" t="s">
         <v>480</v>
       </c>
       <c r="C485" s="7" t="s">
@@ -8560,7 +8583,7 @@
       <c r="A486" s="24">
         <v>8055</v>
       </c>
-      <c r="B486" s="50" t="s">
+      <c r="B486" s="49" t="s">
         <v>481</v>
       </c>
       <c r="C486" s="7" t="s">
@@ -8571,7 +8594,7 @@
       <c r="A487" s="24">
         <v>7582</v>
       </c>
-      <c r="B487" s="50" t="s">
+      <c r="B487" s="49" t="s">
         <v>482</v>
       </c>
       <c r="C487" s="7" t="s">
@@ -8582,7 +8605,7 @@
       <c r="A488" s="24">
         <v>9276</v>
       </c>
-      <c r="B488" s="50" t="s">
+      <c r="B488" s="49" t="s">
         <v>483</v>
       </c>
       <c r="C488" s="7" t="s">
@@ -8593,7 +8616,7 @@
       <c r="A489" s="24">
         <v>6990</v>
       </c>
-      <c r="B489" s="50" t="s">
+      <c r="B489" s="49" t="s">
         <v>484</v>
       </c>
       <c r="C489" s="7" t="s">
@@ -8604,7 +8627,7 @@
       <c r="A490" s="24">
         <v>6807</v>
       </c>
-      <c r="B490" s="50" t="s">
+      <c r="B490" s="49" t="s">
         <v>485</v>
       </c>
       <c r="C490" s="7" t="s">
@@ -8615,7 +8638,7 @@
       <c r="A491" s="24">
         <v>9188</v>
       </c>
-      <c r="B491" s="50" t="s">
+      <c r="B491" s="49" t="s">
         <v>486</v>
       </c>
       <c r="C491" s="7" t="s">
@@ -8626,7 +8649,7 @@
       <c r="A492" s="24">
         <v>9611</v>
       </c>
-      <c r="B492" s="50" t="s">
+      <c r="B492" s="49" t="s">
         <v>398</v>
       </c>
       <c r="C492" s="7" t="s">
@@ -8637,7 +8660,7 @@
       <c r="A493" s="24">
         <v>6817</v>
       </c>
-      <c r="B493" s="50" t="s">
+      <c r="B493" s="49" t="s">
         <v>487</v>
       </c>
       <c r="C493" s="7" t="s">
@@ -8648,7 +8671,7 @@
       <c r="A494" s="24">
         <v>6810</v>
       </c>
-      <c r="B494" s="50" t="s">
+      <c r="B494" s="49" t="s">
         <v>488</v>
       </c>
       <c r="C494" s="7" t="s">
@@ -8659,7 +8682,7 @@
       <c r="A495" s="24">
         <v>8680</v>
       </c>
-      <c r="B495" s="50" t="s">
+      <c r="B495" s="49" t="s">
         <v>489</v>
       </c>
       <c r="C495" s="7" t="s">
@@ -8670,7 +8693,7 @@
       <c r="A496" s="24">
         <v>8368</v>
       </c>
-      <c r="B496" s="50" t="s">
+      <c r="B496" s="49" t="s">
         <v>490</v>
       </c>
       <c r="C496" s="7" t="s">
@@ -8681,7 +8704,7 @@
       <c r="A497" s="24">
         <v>8124</v>
       </c>
-      <c r="B497" s="50" t="s">
+      <c r="B497" s="49" t="s">
         <v>491</v>
       </c>
       <c r="C497" s="7" t="s">
@@ -8692,7 +8715,7 @@
       <c r="A498" s="24">
         <v>8161</v>
       </c>
-      <c r="B498" s="50" t="s">
+      <c r="B498" s="49" t="s">
         <v>492</v>
       </c>
       <c r="C498" s="7" t="s">
@@ -8703,7 +8726,7 @@
       <c r="A499" s="24">
         <v>9401</v>
       </c>
-      <c r="B499" s="50" t="s">
+      <c r="B499" s="49" t="s">
         <v>493</v>
       </c>
       <c r="C499" s="7" t="s">
@@ -8714,7 +8737,7 @@
       <c r="A500" s="24">
         <v>8884</v>
       </c>
-      <c r="B500" s="50" t="s">
+      <c r="B500" s="49" t="s">
         <v>494</v>
       </c>
       <c r="C500" s="7" t="s">
@@ -8857,7 +8880,7 @@
       <c r="A513" s="30">
         <v>9555</v>
       </c>
-      <c r="B513" s="51" t="s">
+      <c r="B513" s="50" t="s">
         <v>505</v>
       </c>
       <c r="C513" s="6" t="s">
@@ -8868,7 +8891,7 @@
       <c r="A514" s="32">
         <v>8746</v>
       </c>
-      <c r="B514" s="51" t="s">
+      <c r="B514" s="50" t="s">
         <v>506</v>
       </c>
       <c r="C514" s="6" t="s">
@@ -8879,7 +8902,7 @@
       <c r="A515" s="30">
         <v>9262</v>
       </c>
-      <c r="B515" s="51" t="s">
+      <c r="B515" s="50" t="s">
         <v>507</v>
       </c>
       <c r="C515" s="6" t="s">
@@ -8890,7 +8913,7 @@
       <c r="A516" s="32">
         <v>8286</v>
       </c>
-      <c r="B516" s="51" t="s">
+      <c r="B516" s="50" t="s">
         <v>508</v>
       </c>
       <c r="C516" s="6" t="s">
@@ -8901,7 +8924,7 @@
       <c r="A517" s="32">
         <v>6398</v>
       </c>
-      <c r="B517" s="51" t="s">
+      <c r="B517" s="50" t="s">
         <v>509</v>
       </c>
       <c r="C517" s="6" t="s">
@@ -8912,7 +8935,7 @@
       <c r="A518" s="30">
         <v>7673</v>
       </c>
-      <c r="B518" s="51" t="s">
+      <c r="B518" s="50" t="s">
         <v>100</v>
       </c>
       <c r="C518" s="6" t="s">
@@ -8923,7 +8946,7 @@
       <c r="A519" s="32">
         <v>9080</v>
       </c>
-      <c r="B519" s="51" t="s">
+      <c r="B519" s="50" t="s">
         <v>409</v>
       </c>
       <c r="C519" s="6" t="s">
@@ -8934,7 +8957,7 @@
       <c r="A520" s="32">
         <v>6231</v>
       </c>
-      <c r="B520" s="51" t="s">
+      <c r="B520" s="50" t="s">
         <v>510</v>
       </c>
       <c r="C520" s="6" t="s">
@@ -8945,7 +8968,7 @@
       <c r="A521" s="32">
         <v>7753</v>
       </c>
-      <c r="B521" s="51" t="s">
+      <c r="B521" s="50" t="s">
         <v>511</v>
       </c>
       <c r="C521" s="6" t="s">
@@ -8956,7 +8979,7 @@
       <c r="A522" s="32">
         <v>8725</v>
       </c>
-      <c r="B522" s="51" t="s">
+      <c r="B522" s="50" t="s">
         <v>512</v>
       </c>
       <c r="C522" s="6" t="s">
@@ -8967,7 +8990,7 @@
       <c r="A523" s="32">
         <v>6963</v>
       </c>
-      <c r="B523" s="51" t="s">
+      <c r="B523" s="50" t="s">
         <v>513</v>
       </c>
       <c r="C523" s="6" t="s">
@@ -8978,7 +9001,7 @@
       <c r="A524" s="32">
         <v>7894</v>
       </c>
-      <c r="B524" s="51" t="s">
+      <c r="B524" s="50" t="s">
         <v>514</v>
       </c>
       <c r="C524" s="6" t="s">
@@ -8989,7 +9012,7 @@
       <c r="A525" s="32">
         <v>6319</v>
       </c>
-      <c r="B525" s="51" t="s">
+      <c r="B525" s="50" t="s">
         <v>515</v>
       </c>
       <c r="C525" s="6" t="s">
@@ -9000,7 +9023,7 @@
       <c r="A526" s="32">
         <v>6434</v>
       </c>
-      <c r="B526" s="51" t="s">
+      <c r="B526" s="50" t="s">
         <v>516</v>
       </c>
       <c r="C526" s="6" t="s">
@@ -9011,7 +9034,7 @@
       <c r="A527" s="32">
         <v>6937</v>
       </c>
-      <c r="B527" s="51" t="s">
+      <c r="B527" s="50" t="s">
         <v>517</v>
       </c>
       <c r="C527" s="6" t="s">
@@ -9022,7 +9045,7 @@
       <c r="A528" s="32">
         <v>6156</v>
       </c>
-      <c r="B528" s="51" t="s">
+      <c r="B528" s="50" t="s">
         <v>518</v>
       </c>
       <c r="C528" s="6" t="s">
@@ -9033,7 +9056,7 @@
       <c r="A529" s="32">
         <v>8457</v>
       </c>
-      <c r="B529" s="51" t="s">
+      <c r="B529" s="50" t="s">
         <v>321</v>
       </c>
       <c r="C529" s="6" t="s">
@@ -9044,7 +9067,7 @@
       <c r="A530" s="32">
         <v>8706</v>
       </c>
-      <c r="B530" s="51" t="s">
+      <c r="B530" s="50" t="s">
         <v>519</v>
       </c>
       <c r="C530" s="6" t="s">
@@ -9055,7 +9078,7 @@
       <c r="A531" s="32">
         <v>9075</v>
       </c>
-      <c r="B531" s="51" t="s">
+      <c r="B531" s="50" t="s">
         <v>520</v>
       </c>
       <c r="C531" s="6" t="s">
@@ -9066,7 +9089,7 @@
       <c r="A532" s="30">
         <v>6223</v>
       </c>
-      <c r="B532" s="51" t="s">
+      <c r="B532" s="50" t="s">
         <v>521</v>
       </c>
       <c r="C532" s="6" t="s">
@@ -9077,7 +9100,7 @@
       <c r="A533" s="30">
         <v>6607</v>
       </c>
-      <c r="B533" s="51" t="s">
+      <c r="B533" s="50" t="s">
         <v>522</v>
       </c>
       <c r="C533" s="6" t="s">
@@ -9088,7 +9111,7 @@
       <c r="A534" s="32">
         <v>8000</v>
       </c>
-      <c r="B534" s="51" t="s">
+      <c r="B534" s="50" t="s">
         <v>523</v>
       </c>
       <c r="C534" s="6" t="s">
@@ -9099,7 +9122,7 @@
       <c r="A535" s="32">
         <v>7494</v>
       </c>
-      <c r="B535" s="51" t="s">
+      <c r="B535" s="50" t="s">
         <v>524</v>
       </c>
       <c r="C535" s="6" t="s">
@@ -9110,7 +9133,7 @@
       <c r="A536" s="32">
         <v>6661</v>
       </c>
-      <c r="B536" s="51" t="s">
+      <c r="B536" s="50" t="s">
         <v>525</v>
       </c>
       <c r="C536" s="6" t="s">
@@ -9121,7 +9144,7 @@
       <c r="A537" s="32">
         <v>7272</v>
       </c>
-      <c r="B537" s="51" t="s">
+      <c r="B537" s="50" t="s">
         <v>526</v>
       </c>
       <c r="C537" s="6" t="s">
@@ -9132,7 +9155,7 @@
       <c r="A538" s="32">
         <v>6449</v>
       </c>
-      <c r="B538" s="51" t="s">
+      <c r="B538" s="50" t="s">
         <v>527</v>
       </c>
       <c r="C538" s="6" t="s">
@@ -9143,7 +9166,7 @@
       <c r="A539" s="30">
         <v>6604</v>
       </c>
-      <c r="B539" s="51" t="s">
+      <c r="B539" s="50" t="s">
         <v>528</v>
       </c>
       <c r="C539" s="6" t="s">
@@ -9154,7 +9177,7 @@
       <c r="A540" s="30">
         <v>6485</v>
       </c>
-      <c r="B540" s="51" t="s">
+      <c r="B540" s="50" t="s">
         <v>529</v>
       </c>
       <c r="C540" s="6" t="s">
@@ -9165,7 +9188,7 @@
       <c r="A541" s="30">
         <v>9059</v>
       </c>
-      <c r="B541" s="51" t="s">
+      <c r="B541" s="50" t="s">
         <v>530</v>
       </c>
       <c r="C541" s="6" t="s">
@@ -9176,7 +9199,7 @@
       <c r="A542" s="30">
         <v>7911</v>
       </c>
-      <c r="B542" s="51" t="s">
+      <c r="B542" s="50" t="s">
         <v>72</v>
       </c>
       <c r="C542" s="6" t="s">
@@ -9187,7 +9210,7 @@
       <c r="A543" s="32">
         <v>6936</v>
       </c>
-      <c r="B543" s="51" t="s">
+      <c r="B543" s="50" t="s">
         <v>531</v>
       </c>
       <c r="C543" s="6" t="s">
@@ -9198,7 +9221,7 @@
       <c r="A544" s="32">
         <v>5883</v>
       </c>
-      <c r="B544" s="51" t="s">
+      <c r="B544" s="50" t="s">
         <v>532</v>
       </c>
       <c r="C544" s="6" t="s">
@@ -9209,7 +9232,7 @@
       <c r="A545" s="32">
         <v>6016</v>
       </c>
-      <c r="B545" s="51" t="s">
+      <c r="B545" s="50" t="s">
         <v>533</v>
       </c>
       <c r="C545" s="6" t="s">
@@ -9220,7 +9243,7 @@
       <c r="A546" s="32">
         <v>9180</v>
       </c>
-      <c r="B546" s="51" t="s">
+      <c r="B546" s="50" t="s">
         <v>534</v>
       </c>
       <c r="C546" s="6" t="s">
@@ -9231,7 +9254,7 @@
       <c r="A547" s="32">
         <v>7031</v>
       </c>
-      <c r="B547" s="51" t="s">
+      <c r="B547" s="50" t="s">
         <v>535</v>
       </c>
       <c r="C547" s="6" t="s">
@@ -9242,7 +9265,7 @@
       <c r="A548" s="32">
         <v>6741</v>
       </c>
-      <c r="B548" s="51" t="s">
+      <c r="B548" s="50" t="s">
         <v>536</v>
       </c>
       <c r="C548" s="6" t="s">
@@ -9253,7 +9276,7 @@
       <c r="A549" s="32">
         <v>5918</v>
       </c>
-      <c r="B549" s="51" t="s">
+      <c r="B549" s="50" t="s">
         <v>537</v>
       </c>
       <c r="C549" s="6" t="s">
@@ -9264,7 +9287,7 @@
       <c r="A550" s="32">
         <v>5814</v>
       </c>
-      <c r="B550" s="51" t="s">
+      <c r="B550" s="50" t="s">
         <v>538</v>
       </c>
       <c r="C550" s="6" t="s">
@@ -9275,7 +9298,7 @@
       <c r="A551" s="32">
         <v>5892</v>
       </c>
-      <c r="B551" s="51" t="s">
+      <c r="B551" s="50" t="s">
         <v>539</v>
       </c>
       <c r="C551" s="6" t="s">
@@ -9286,7 +9309,7 @@
       <c r="A552" s="32">
         <v>8112</v>
       </c>
-      <c r="B552" s="51" t="s">
+      <c r="B552" s="50" t="s">
         <v>540</v>
       </c>
       <c r="C552" s="6" t="s">
@@ -9297,7 +9320,7 @@
       <c r="A553" s="30">
         <v>5852</v>
       </c>
-      <c r="B553" s="51" t="s">
+      <c r="B553" s="50" t="s">
         <v>541</v>
       </c>
       <c r="C553" s="6" t="s">
@@ -9308,7 +9331,7 @@
       <c r="A554" s="30">
         <v>5843</v>
       </c>
-      <c r="B554" s="51" t="s">
+      <c r="B554" s="50" t="s">
         <v>542</v>
       </c>
       <c r="C554" s="6" t="s">
@@ -9319,7 +9342,7 @@
       <c r="A555" s="32">
         <v>6775</v>
       </c>
-      <c r="B555" s="51" t="s">
+      <c r="B555" s="50" t="s">
         <v>543</v>
       </c>
       <c r="C555" s="6" t="s">
@@ -9330,7 +9353,7 @@
       <c r="A556" s="32">
         <v>5881</v>
       </c>
-      <c r="B556" s="51" t="s">
+      <c r="B556" s="50" t="s">
         <v>544</v>
       </c>
       <c r="C556" s="6" t="s">
@@ -9341,7 +9364,7 @@
       <c r="A557" s="32">
         <v>8990</v>
       </c>
-      <c r="B557" s="51" t="s">
+      <c r="B557" s="50" t="s">
         <v>110</v>
       </c>
       <c r="C557" s="6" t="s">
@@ -9352,7 +9375,7 @@
       <c r="A558" s="32">
         <v>5856</v>
       </c>
-      <c r="B558" s="51" t="s">
+      <c r="B558" s="50" t="s">
         <v>545</v>
       </c>
       <c r="C558" s="6" t="s">
@@ -9363,7 +9386,7 @@
       <c r="A559" s="32">
         <v>5846</v>
       </c>
-      <c r="B559" s="51" t="s">
+      <c r="B559" s="50" t="s">
         <v>546</v>
       </c>
       <c r="C559" s="6" t="s">
@@ -9374,7 +9397,7 @@
       <c r="A560" s="32">
         <v>9419</v>
       </c>
-      <c r="B560" s="51" t="s">
+      <c r="B560" s="50" t="s">
         <v>547</v>
       </c>
       <c r="C560" s="6" t="s">
@@ -9385,7 +9408,7 @@
       <c r="A561" s="32">
         <v>9419</v>
       </c>
-      <c r="B561" s="51" t="s">
+      <c r="B561" s="50" t="s">
         <v>548</v>
       </c>
       <c r="C561" s="6" t="s">
@@ -9396,7 +9419,7 @@
       <c r="A562" s="32">
         <v>5988</v>
       </c>
-      <c r="B562" s="51" t="s">
+      <c r="B562" s="50" t="s">
         <v>549</v>
       </c>
       <c r="C562" s="6" t="s">
@@ -9407,7 +9430,7 @@
       <c r="A563" s="30">
         <v>5849</v>
       </c>
-      <c r="B563" s="51" t="s">
+      <c r="B563" s="50" t="s">
         <v>550</v>
       </c>
       <c r="C563" s="6" t="s">
@@ -9418,7 +9441,7 @@
       <c r="A564" s="32">
         <v>7257</v>
       </c>
-      <c r="B564" s="51" t="s">
+      <c r="B564" s="50" t="s">
         <v>56</v>
       </c>
       <c r="C564" s="6" t="s">
@@ -9429,7 +9452,7 @@
       <c r="A565" s="32">
         <v>7215</v>
       </c>
-      <c r="B565" s="51" t="s">
+      <c r="B565" s="50" t="s">
         <v>551</v>
       </c>
       <c r="C565" s="6" t="s">
@@ -9440,7 +9463,7 @@
       <c r="A566" s="32">
         <v>8453</v>
       </c>
-      <c r="B566" s="51" t="s">
+      <c r="B566" s="50" t="s">
         <v>380</v>
       </c>
       <c r="C566" s="6" t="s">
@@ -9451,7 +9474,7 @@
       <c r="A567" s="32">
         <v>7784</v>
       </c>
-      <c r="B567" s="51" t="s">
+      <c r="B567" s="50" t="s">
         <v>552</v>
       </c>
       <c r="C567" s="6" t="s">
@@ -9462,7 +9485,7 @@
       <c r="A568" s="32">
         <v>9089</v>
       </c>
-      <c r="B568" s="51" t="s">
+      <c r="B568" s="50" t="s">
         <v>553</v>
       </c>
       <c r="C568" s="6" t="s">
@@ -9473,7 +9496,7 @@
       <c r="A569" s="32">
         <v>9624</v>
       </c>
-      <c r="B569" s="51" t="s">
+      <c r="B569" s="50" t="s">
         <v>554</v>
       </c>
       <c r="C569" s="6" t="s">
@@ -9484,7 +9507,7 @@
       <c r="A570" s="32">
         <v>5875</v>
       </c>
-      <c r="B570" s="51" t="s">
+      <c r="B570" s="50" t="s">
         <v>555</v>
       </c>
       <c r="C570" s="6" t="s">
@@ -9495,7 +9518,7 @@
       <c r="A571" s="32">
         <v>7550</v>
       </c>
-      <c r="B571" s="51" t="s">
+      <c r="B571" s="50" t="s">
         <v>556</v>
       </c>
       <c r="C571" s="6" t="s">
@@ -9506,7 +9529,7 @@
       <c r="A572" s="30">
         <v>9105</v>
       </c>
-      <c r="B572" s="51" t="s">
+      <c r="B572" s="50" t="s">
         <v>557</v>
       </c>
       <c r="C572" s="6" t="s">
@@ -9517,7 +9540,7 @@
       <c r="A573" s="32">
         <v>7773</v>
       </c>
-      <c r="B573" s="51" t="s">
+      <c r="B573" s="50" t="s">
         <v>558</v>
       </c>
       <c r="C573" s="6" t="s">
@@ -9528,7 +9551,7 @@
       <c r="A574" s="32">
         <v>8588</v>
       </c>
-      <c r="B574" s="51" t="s">
+      <c r="B574" s="50" t="s">
         <v>559</v>
       </c>
       <c r="C574" s="6" t="s">
@@ -9539,7 +9562,7 @@
       <c r="A575" s="32">
         <v>9015</v>
       </c>
-      <c r="B575" s="51" t="s">
+      <c r="B575" s="50" t="s">
         <v>560</v>
       </c>
       <c r="C575" s="6" t="s">
@@ -9550,7 +9573,7 @@
       <c r="A576" s="30">
         <v>7646</v>
       </c>
-      <c r="B576" s="51" t="s">
+      <c r="B576" s="50" t="s">
         <v>561</v>
       </c>
       <c r="C576" s="6" t="s">
@@ -9561,7 +9584,7 @@
       <c r="A577" s="30">
         <v>7801</v>
       </c>
-      <c r="B577" s="51" t="s">
+      <c r="B577" s="50" t="s">
         <v>144</v>
       </c>
       <c r="C577" s="6" t="s">
@@ -9572,7 +9595,7 @@
       <c r="A578" s="30">
         <v>8072</v>
       </c>
-      <c r="B578" s="51" t="s">
+      <c r="B578" s="50" t="s">
         <v>102</v>
       </c>
       <c r="C578" s="6" t="s">
@@ -9583,7 +9606,7 @@
       <c r="A579" s="30">
         <v>9193</v>
       </c>
-      <c r="B579" s="51" t="s">
+      <c r="B579" s="50" t="s">
         <v>562</v>
       </c>
       <c r="C579" s="6" t="s">
@@ -9594,7 +9617,7 @@
       <c r="A580" s="30">
         <v>7975</v>
       </c>
-      <c r="B580" s="51" t="s">
+      <c r="B580" s="50" t="s">
         <v>563</v>
       </c>
       <c r="C580" s="6" t="s">
@@ -9605,7 +9628,7 @@
       <c r="A581" s="32">
         <v>5625</v>
       </c>
-      <c r="B581" s="51" t="s">
+      <c r="B581" s="50" t="s">
         <v>3</v>
       </c>
       <c r="C581" s="6" t="s">
@@ -9616,7 +9639,7 @@
       <c r="A582" s="32">
         <v>5541</v>
       </c>
-      <c r="B582" s="51" t="s">
+      <c r="B582" s="50" t="s">
         <v>564</v>
       </c>
       <c r="C582" s="6" t="s">
@@ -9627,7 +9650,7 @@
       <c r="A583" s="32">
         <v>7183</v>
       </c>
-      <c r="B583" s="51" t="s">
+      <c r="B583" s="50" t="s">
         <v>565</v>
       </c>
       <c r="C583" s="6" t="s">
@@ -9638,7 +9661,7 @@
       <c r="A584" s="32">
         <v>5265</v>
       </c>
-      <c r="B584" s="51" t="s">
+      <c r="B584" s="50" t="s">
         <v>566</v>
       </c>
       <c r="C584" s="6" t="s">
@@ -9649,7 +9672,7 @@
       <c r="A585" s="30">
         <v>5640</v>
       </c>
-      <c r="B585" s="51" t="s">
+      <c r="B585" s="50" t="s">
         <v>567</v>
       </c>
       <c r="C585" s="6" t="s">
@@ -9660,7 +9683,7 @@
       <c r="A586" s="30">
         <v>6672</v>
       </c>
-      <c r="B586" s="51" t="s">
+      <c r="B586" s="50" t="s">
         <v>568</v>
       </c>
       <c r="C586" s="6" t="s">
@@ -9671,7 +9694,7 @@
       <c r="A587" s="32">
         <v>5607</v>
       </c>
-      <c r="B587" s="51" t="s">
+      <c r="B587" s="50" t="s">
         <v>569</v>
       </c>
       <c r="C587" s="6" t="s">
@@ -9682,7 +9705,7 @@
       <c r="A588" s="32">
         <v>7516</v>
       </c>
-      <c r="B588" s="51" t="s">
+      <c r="B588" s="50" t="s">
         <v>4</v>
       </c>
       <c r="C588" s="6" t="s">
@@ -9693,7 +9716,7 @@
       <c r="A589" s="32">
         <v>7174</v>
       </c>
-      <c r="B589" s="51" t="s">
+      <c r="B589" s="50" t="s">
         <v>570</v>
       </c>
       <c r="C589" s="6" t="s">
@@ -9704,7 +9727,7 @@
       <c r="A590" s="32">
         <v>8001</v>
       </c>
-      <c r="B590" s="51" t="s">
+      <c r="B590" s="50" t="s">
         <v>571</v>
       </c>
       <c r="C590" s="6" t="s">
@@ -9715,7 +9738,7 @@
       <c r="A591" s="32">
         <v>7779</v>
       </c>
-      <c r="B591" s="51" t="s">
+      <c r="B591" s="50" t="s">
         <v>572</v>
       </c>
       <c r="C591" s="6" t="s">
@@ -9726,7 +9749,7 @@
       <c r="A592" s="32">
         <v>7626</v>
       </c>
-      <c r="B592" s="51" t="s">
+      <c r="B592" s="50" t="s">
         <v>573</v>
       </c>
       <c r="C592" s="6" t="s">
@@ -9737,7 +9760,7 @@
       <c r="A593" s="32">
         <v>5526</v>
       </c>
-      <c r="B593" s="51" t="s">
+      <c r="B593" s="50" t="s">
         <v>574</v>
       </c>
       <c r="C593" s="6" t="s">
@@ -9748,7 +9771,7 @@
       <c r="A594" s="32">
         <v>7577</v>
       </c>
-      <c r="B594" s="51" t="s">
+      <c r="B594" s="50" t="s">
         <v>575</v>
       </c>
       <c r="C594" s="6" t="s">
@@ -9759,7 +9782,7 @@
       <c r="A595" s="32">
         <v>6435</v>
       </c>
-      <c r="B595" s="51" t="s">
+      <c r="B595" s="50" t="s">
         <v>576</v>
       </c>
       <c r="C595" s="6" t="s">
@@ -9770,7 +9793,7 @@
       <c r="A596" s="32">
         <v>7350</v>
       </c>
-      <c r="B596" s="51" t="s">
+      <c r="B596" s="50" t="s">
         <v>426</v>
       </c>
       <c r="C596" s="6" t="s">
@@ -9781,7 +9804,7 @@
       <c r="A597" s="32">
         <v>5386</v>
       </c>
-      <c r="B597" s="51" t="s">
+      <c r="B597" s="50" t="s">
         <v>577</v>
       </c>
       <c r="C597" s="6" t="s">
@@ -9792,7 +9815,7 @@
       <c r="A598" s="32">
         <v>7810</v>
       </c>
-      <c r="B598" s="51" t="s">
+      <c r="B598" s="50" t="s">
         <v>578</v>
       </c>
       <c r="C598" s="6" t="s">
@@ -9803,7 +9826,7 @@
       <c r="A599" s="32">
         <v>5785</v>
       </c>
-      <c r="B599" s="51" t="s">
+      <c r="B599" s="50" t="s">
         <v>579</v>
       </c>
       <c r="C599" s="6" t="s">
@@ -9814,7 +9837,7 @@
       <c r="A600" s="32">
         <v>8502</v>
       </c>
-      <c r="B600" s="51" t="s">
+      <c r="B600" s="50" t="s">
         <v>580</v>
       </c>
       <c r="C600" s="6" t="s">
@@ -9825,7 +9848,7 @@
       <c r="A601" s="32">
         <v>4941</v>
       </c>
-      <c r="B601" s="51" t="s">
+      <c r="B601" s="50" t="s">
         <v>581</v>
       </c>
       <c r="C601" s="6" t="s">
@@ -9836,7 +9859,7 @@
       <c r="A602" s="32">
         <v>5674</v>
       </c>
-      <c r="B602" s="51" t="s">
+      <c r="B602" s="50" t="s">
         <v>582</v>
       </c>
       <c r="C602" s="6" t="s">
@@ -9847,7 +9870,7 @@
       <c r="A603" s="32">
         <v>8552</v>
       </c>
-      <c r="B603" s="51" t="s">
+      <c r="B603" s="50" t="s">
         <v>583</v>
       </c>
       <c r="C603" s="6" t="s">
@@ -9858,7 +9881,7 @@
       <c r="A604" s="33">
         <v>9450</v>
       </c>
-      <c r="B604" s="52" t="s">
+      <c r="B604" s="51" t="s">
         <v>584</v>
       </c>
       <c r="C604" s="6" t="s">
@@ -9869,7 +9892,7 @@
       <c r="A605" s="33">
         <v>9031</v>
       </c>
-      <c r="B605" s="52" t="s">
+      <c r="B605" s="51" t="s">
         <v>3</v>
       </c>
       <c r="C605" s="6" t="s">
@@ -9880,7 +9903,7 @@
       <c r="A606" s="33">
         <v>9106</v>
       </c>
-      <c r="B606" s="52" t="s">
+      <c r="B606" s="51" t="s">
         <v>585</v>
       </c>
       <c r="C606" s="6" t="s">
@@ -9891,7 +9914,7 @@
       <c r="A607" s="33">
         <v>8068</v>
       </c>
-      <c r="B607" s="52" t="s">
+      <c r="B607" s="51" t="s">
         <v>586</v>
       </c>
       <c r="C607" s="6" t="s">
@@ -9902,7 +9925,7 @@
       <c r="A608" s="33">
         <v>7518</v>
       </c>
-      <c r="B608" s="52" t="s">
+      <c r="B608" s="51" t="s">
         <v>587</v>
       </c>
       <c r="C608" s="6" t="s">
@@ -9913,7 +9936,7 @@
       <c r="A609" s="33">
         <v>8658</v>
       </c>
-      <c r="B609" s="52" t="s">
+      <c r="B609" s="51" t="s">
         <v>588</v>
       </c>
       <c r="C609" s="6" t="s">
@@ -9924,7 +9947,7 @@
       <c r="A610" s="33">
         <v>6153</v>
       </c>
-      <c r="B610" s="52" t="s">
+      <c r="B610" s="51" t="s">
         <v>589</v>
       </c>
       <c r="C610" s="6" t="s">
@@ -9935,7 +9958,7 @@
       <c r="A611" s="33">
         <v>7527</v>
       </c>
-      <c r="B611" s="52" t="s">
+      <c r="B611" s="51" t="s">
         <v>590</v>
       </c>
       <c r="C611" s="6" t="s">
@@ -9946,7 +9969,7 @@
       <c r="A612" s="33">
         <v>8917</v>
       </c>
-      <c r="B612" s="52" t="s">
+      <c r="B612" s="51" t="s">
         <v>591</v>
       </c>
       <c r="C612" s="6" t="s">
@@ -9957,7 +9980,7 @@
       <c r="A613" s="33">
         <v>6276</v>
       </c>
-      <c r="B613" s="52" t="s">
+      <c r="B613" s="51" t="s">
         <v>592</v>
       </c>
       <c r="C613" s="6" t="s">
@@ -9968,7 +9991,7 @@
       <c r="A614" s="33">
         <v>8397</v>
       </c>
-      <c r="B614" s="52" t="s">
+      <c r="B614" s="51" t="s">
         <v>475</v>
       </c>
       <c r="C614" s="6" t="s">
@@ -9979,7 +10002,7 @@
       <c r="A615" s="33">
         <v>6184</v>
       </c>
-      <c r="B615" s="52" t="s">
+      <c r="B615" s="51" t="s">
         <v>385</v>
       </c>
       <c r="C615" s="6" t="s">
@@ -9990,7 +10013,7 @@
       <c r="A616" s="33">
         <v>7637</v>
       </c>
-      <c r="B616" s="52" t="s">
+      <c r="B616" s="51" t="s">
         <v>593</v>
       </c>
       <c r="C616" s="6" t="s">
@@ -10001,7 +10024,7 @@
       <c r="A617" s="33">
         <v>7791</v>
       </c>
-      <c r="B617" s="52" t="s">
+      <c r="B617" s="51" t="s">
         <v>594</v>
       </c>
       <c r="C617" s="6" t="s">
@@ -10012,7 +10035,7 @@
       <c r="A618" s="33">
         <v>5284</v>
       </c>
-      <c r="B618" s="52" t="s">
+      <c r="B618" s="51" t="s">
         <v>595</v>
       </c>
       <c r="C618" s="6" t="s">
@@ -10023,7 +10046,7 @@
       <c r="A619" s="33">
         <v>9606</v>
       </c>
-      <c r="B619" s="52" t="s">
+      <c r="B619" s="51" t="s">
         <v>596</v>
       </c>
       <c r="C619" s="6" t="s">
@@ -10034,7 +10057,7 @@
       <c r="A620" s="33">
         <v>5330</v>
       </c>
-      <c r="B620" s="52" t="s">
+      <c r="B620" s="51" t="s">
         <v>597</v>
       </c>
       <c r="C620" s="6" t="s">
@@ -10045,7 +10068,7 @@
       <c r="A621" s="33">
         <v>7912</v>
       </c>
-      <c r="B621" s="52" t="s">
+      <c r="B621" s="51" t="s">
         <v>598</v>
       </c>
       <c r="C621" s="6" t="s">
@@ -10056,7 +10079,7 @@
       <c r="A622" s="33">
         <v>5296</v>
       </c>
-      <c r="B622" s="52" t="s">
+      <c r="B622" s="51" t="s">
         <v>599</v>
       </c>
       <c r="C622" s="6" t="s">
@@ -10064,10 +10087,10 @@
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A623" s="55">
+      <c r="A623" s="54">
         <v>5262</v>
       </c>
-      <c r="B623" s="56" t="s">
+      <c r="B623" s="55" t="s">
         <v>426</v>
       </c>
       <c r="C623" s="6" t="s">
@@ -10075,340 +10098,340 @@
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A624" s="57">
+      <c r="A624" s="56">
         <v>6834</v>
       </c>
-      <c r="B624" s="58" t="s">
+      <c r="B624" s="57" t="s">
         <v>600</v>
       </c>
-      <c r="C624" s="57" t="s">
+      <c r="C624" s="56" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A625" s="57">
+      <c r="A625" s="56">
         <v>9537</v>
       </c>
-      <c r="B625" s="58" t="s">
+      <c r="B625" s="57" t="s">
         <v>601</v>
       </c>
-      <c r="C625" s="57" t="s">
+      <c r="C625" s="56" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A626" s="57">
+      <c r="A626" s="56">
         <v>6676</v>
       </c>
-      <c r="B626" s="58" t="s">
+      <c r="B626" s="57" t="s">
         <v>602</v>
       </c>
-      <c r="C626" s="57" t="s">
+      <c r="C626" s="56" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A627" s="57">
+      <c r="A627" s="56">
         <v>6342</v>
       </c>
-      <c r="B627" s="58" t="s">
+      <c r="B627" s="57" t="s">
         <v>603</v>
       </c>
-      <c r="C627" s="57" t="s">
+      <c r="C627" s="56" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A628" s="57">
+      <c r="A628" s="56">
         <v>9089</v>
       </c>
-      <c r="B628" s="58" t="s">
+      <c r="B628" s="57" t="s">
         <v>304</v>
       </c>
-      <c r="C628" s="57" t="s">
+      <c r="C628" s="56" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A629" s="57">
+      <c r="A629" s="56">
         <v>7331</v>
       </c>
-      <c r="B629" s="58" t="s">
+      <c r="B629" s="57" t="s">
         <v>604</v>
       </c>
-      <c r="C629" s="57" t="s">
+      <c r="C629" s="56" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A630" s="57">
+      <c r="A630" s="56">
         <v>9032</v>
       </c>
-      <c r="B630" s="58" t="s">
+      <c r="B630" s="57" t="s">
         <v>605</v>
       </c>
-      <c r="C630" s="57" t="s">
+      <c r="C630" s="56" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A631" s="57">
+      <c r="A631" s="56">
         <v>6140</v>
       </c>
-      <c r="B631" s="58" t="s">
+      <c r="B631" s="57" t="s">
         <v>606</v>
       </c>
-      <c r="C631" s="57" t="s">
+      <c r="C631" s="56" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A632" s="57">
+      <c r="A632" s="56">
         <v>6266</v>
       </c>
-      <c r="B632" s="58" t="s">
+      <c r="B632" s="57" t="s">
         <v>513</v>
       </c>
-      <c r="C632" s="57" t="s">
+      <c r="C632" s="56" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A633" s="57">
+      <c r="A633" s="56">
         <v>8314</v>
       </c>
-      <c r="B633" s="58" t="s">
+      <c r="B633" s="57" t="s">
         <v>607</v>
       </c>
-      <c r="C633" s="57" t="s">
+      <c r="C633" s="56" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A634" s="57">
+      <c r="A634" s="56">
         <v>8216</v>
       </c>
-      <c r="B634" s="58" t="s">
+      <c r="B634" s="57" t="s">
         <v>608</v>
       </c>
-      <c r="C634" s="57" t="s">
+      <c r="C634" s="56" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A635" s="57">
+      <c r="A635" s="56">
         <v>6820</v>
       </c>
-      <c r="B635" s="58" t="s">
+      <c r="B635" s="57" t="s">
         <v>609</v>
       </c>
-      <c r="C635" s="57" t="s">
+      <c r="C635" s="56" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A636" s="57">
+      <c r="A636" s="56">
         <v>5950</v>
       </c>
-      <c r="B636" s="58" t="s">
+      <c r="B636" s="57" t="s">
         <v>610</v>
       </c>
-      <c r="C636" s="57" t="s">
+      <c r="C636" s="56" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A637" s="57">
+      <c r="A637" s="56">
         <v>5297</v>
       </c>
-      <c r="B637" s="58" t="s">
+      <c r="B637" s="57" t="s">
+        <v>725</v>
+      </c>
+      <c r="C637" s="56" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A638" s="58">
+        <v>8265</v>
+      </c>
+      <c r="B638" s="58" t="s">
         <v>611</v>
       </c>
-      <c r="C637" s="57" t="s">
+      <c r="C638" s="59" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A639" s="58">
+        <v>7236</v>
+      </c>
+      <c r="B639" s="58" t="s">
+        <v>612</v>
+      </c>
+      <c r="C639" s="59" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A640" s="58">
+        <v>6261</v>
+      </c>
+      <c r="B640" s="58" t="s">
+        <v>613</v>
+      </c>
+      <c r="C640" s="59" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A641" s="58">
+        <v>6433</v>
+      </c>
+      <c r="B641" s="58" t="s">
+        <v>614</v>
+      </c>
+      <c r="C641" s="59" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A642" s="58">
+        <v>7939</v>
+      </c>
+      <c r="B642" s="58" t="s">
+        <v>519</v>
+      </c>
+      <c r="C642" s="59" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A643" s="58">
+        <v>5832</v>
+      </c>
+      <c r="B643" s="58" t="s">
+        <v>475</v>
+      </c>
+      <c r="C643" s="59" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="638" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A638" s="59">
-        <v>8265</v>
-      </c>
-      <c r="B638" s="59" t="s">
-        <v>612</v>
-      </c>
-      <c r="C638" s="60" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="639" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A639" s="59">
-        <v>7236</v>
-      </c>
-      <c r="B639" s="59" t="s">
-        <v>613</v>
-      </c>
-      <c r="C639" s="60" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A640" s="59">
-        <v>6261</v>
-      </c>
-      <c r="B640" s="59" t="s">
-        <v>614</v>
-      </c>
-      <c r="C640" s="60" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="641" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A641" s="59">
-        <v>6433</v>
-      </c>
-      <c r="B641" s="59" t="s">
+    <row r="644" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A644" s="58">
+        <v>7557</v>
+      </c>
+      <c r="B644" s="58" t="s">
         <v>615</v>
       </c>
-      <c r="C641" s="60" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="642" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A642" s="59">
-        <v>7939</v>
-      </c>
-      <c r="B642" s="59" t="s">
-        <v>519</v>
-      </c>
-      <c r="C642" s="60" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="643" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A643" s="59">
-        <v>5832</v>
-      </c>
-      <c r="B643" s="59" t="s">
-        <v>475</v>
-      </c>
-      <c r="C643" s="60" t="s">
+      <c r="C644" s="59" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="644" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A644" s="59">
-        <v>7557</v>
-      </c>
-      <c r="B644" s="59" t="s">
+    <row r="645" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A645" s="58">
+        <v>8327</v>
+      </c>
+      <c r="B645" s="58" t="s">
         <v>616</v>
       </c>
-      <c r="C644" s="60" t="s">
+      <c r="C645" s="59" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="645" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A645" s="59">
-        <v>8327</v>
-      </c>
-      <c r="B645" s="59" t="s">
+    <row r="646" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A646" s="58">
+        <v>7188</v>
+      </c>
+      <c r="B646" s="58" t="s">
         <v>617</v>
       </c>
-      <c r="C645" s="60" t="s">
+      <c r="C646" s="59" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="646" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A646" s="59">
-        <v>7188</v>
-      </c>
-      <c r="B646" s="59" t="s">
+    <row r="647" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A647" s="58">
+        <v>8805</v>
+      </c>
+      <c r="B647" s="58" t="s">
         <v>618</v>
       </c>
-      <c r="C646" s="60" t="s">
+      <c r="C647" s="59" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="647" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A647" s="59">
-        <v>8805</v>
-      </c>
-      <c r="B647" s="59" t="s">
+    <row r="648" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A648" s="58">
+        <v>6583</v>
+      </c>
+      <c r="B648" s="58" t="s">
         <v>619</v>
       </c>
-      <c r="C647" s="60" t="s">
+      <c r="C648" s="59" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="648" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A648" s="59">
-        <v>6583</v>
-      </c>
-      <c r="B648" s="59" t="s">
+    <row r="649" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A649" s="58">
+        <v>7978</v>
+      </c>
+      <c r="B649" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="C649" s="59" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A650" s="58">
+        <v>5606</v>
+      </c>
+      <c r="B650" s="58" t="s">
         <v>620</v>
       </c>
-      <c r="C648" s="60" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A649" s="59">
-        <v>7978</v>
-      </c>
-      <c r="B649" s="59" t="s">
-        <v>132</v>
-      </c>
-      <c r="C649" s="60" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A650" s="59">
-        <v>5606</v>
-      </c>
-      <c r="B650" s="59" t="s">
+      <c r="C650" s="59" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A651" s="58">
+        <v>5619</v>
+      </c>
+      <c r="B651" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C651" s="59" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A652" s="58">
+        <v>5534</v>
+      </c>
+      <c r="B652" s="58" t="s">
         <v>621</v>
       </c>
-      <c r="C650" s="60" t="s">
+      <c r="C652" s="59" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="651" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A651" s="59">
-        <v>5619</v>
-      </c>
-      <c r="B651" s="59" t="s">
-        <v>397</v>
-      </c>
-      <c r="C651" s="60" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A652" s="59">
-        <v>5534</v>
-      </c>
-      <c r="B652" s="59" t="s">
+    <row r="653" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A653" s="60">
+        <v>4595</v>
+      </c>
+      <c r="B653" s="60" t="s">
         <v>622</v>
       </c>
-      <c r="C652" s="60" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A653" s="61">
-        <v>4595</v>
-      </c>
-      <c r="B653" s="61" t="s">
-        <v>623</v>
-      </c>
-      <c r="C653" s="60" t="s">
+      <c r="C653" s="59" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="654" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A654" s="64">
+      <c r="A654" s="63">
         <v>6554</v>
       </c>
-      <c r="B654" s="62" t="s">
+      <c r="B654" s="61" t="s">
         <v>552</v>
       </c>
       <c r="C654" s="6" t="s">
@@ -10416,362 +10439,362 @@
       </c>
     </row>
     <row r="655" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A655" s="64">
+      <c r="A655" s="63">
         <v>6429</v>
       </c>
-      <c r="B655" s="62" t="s">
-        <v>624</v>
+      <c r="B655" s="61" t="s">
+        <v>623</v>
       </c>
       <c r="C655" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A656" s="64">
+      <c r="A656" s="63">
         <v>7315</v>
       </c>
-      <c r="B656" s="62" t="s">
-        <v>625</v>
+      <c r="B656" s="61" t="s">
+        <v>624</v>
       </c>
       <c r="C656" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A657" s="64">
+      <c r="A657" s="63">
         <v>9517</v>
       </c>
-      <c r="B657" s="62" t="s">
-        <v>626</v>
+      <c r="B657" s="61" t="s">
+        <v>625</v>
       </c>
       <c r="C657" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A658" s="64">
+      <c r="A658" s="63">
         <v>7191</v>
       </c>
-      <c r="B658" s="62" t="s">
-        <v>627</v>
+      <c r="B658" s="61" t="s">
+        <v>626</v>
       </c>
       <c r="C658" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A659" s="64">
+      <c r="A659" s="63">
         <v>6421</v>
       </c>
-      <c r="B659" s="62" t="s">
-        <v>628</v>
+      <c r="B659" s="61" t="s">
+        <v>627</v>
       </c>
       <c r="C659" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A660" s="64">
+      <c r="A660" s="63">
         <v>8888</v>
       </c>
-      <c r="B660" s="62" t="s">
-        <v>629</v>
+      <c r="B660" s="61" t="s">
+        <v>628</v>
       </c>
       <c r="C660" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="661" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A661" s="64">
+      <c r="A661" s="63">
         <v>8666</v>
       </c>
-      <c r="B661" s="62" t="s">
-        <v>630</v>
+      <c r="B661" s="61" t="s">
+        <v>629</v>
       </c>
       <c r="C661" s="6" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="662" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A662" s="64">
+      <c r="A662" s="63">
         <v>6171</v>
       </c>
-      <c r="B662" s="62" t="s">
-        <v>631</v>
+      <c r="B662" s="61" t="s">
+        <v>630</v>
       </c>
       <c r="C662" s="6" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="663" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A663" s="64">
+      <c r="A663" s="63">
         <v>7434</v>
       </c>
-      <c r="B663" s="62" t="s">
-        <v>632</v>
+      <c r="B663" s="61" t="s">
+        <v>631</v>
       </c>
       <c r="C663" s="6" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="664" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A664" s="65">
+      <c r="A664" s="64">
         <v>9660</v>
       </c>
-      <c r="B664" s="66" t="s">
+      <c r="B664" s="65" t="s">
+        <v>632</v>
+      </c>
+      <c r="C664" s="66" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A665" s="62">
+        <v>7597</v>
+      </c>
+      <c r="B665" s="67" t="s">
         <v>633</v>
       </c>
-      <c r="C664" s="67" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A665" s="63">
-        <v>7597</v>
-      </c>
-      <c r="B665" s="68" t="s">
-        <v>634</v>
-      </c>
-      <c r="C665" s="69" t="s">
+      <c r="C665" s="68" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="666" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A666" s="63">
+      <c r="A666" s="62">
         <v>8502</v>
       </c>
-      <c r="B666" s="68" t="s">
+      <c r="B666" s="67" t="s">
         <v>580</v>
       </c>
-      <c r="C666" s="69" t="s">
+      <c r="C666" s="68" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A667" s="70">
+      <c r="A667" s="69">
         <v>6726</v>
       </c>
-      <c r="B667" s="68" t="s">
+      <c r="B667" s="67" t="s">
+        <v>635</v>
+      </c>
+      <c r="C667" s="68" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A668" s="56">
+        <v>8807</v>
+      </c>
+      <c r="B668" s="56" t="s">
         <v>636</v>
-      </c>
-      <c r="C667" s="69" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A668" s="57">
-        <v>8807</v>
-      </c>
-      <c r="B668" s="57" t="s">
-        <v>637</v>
       </c>
       <c r="C668" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A669" s="57">
+      <c r="A669" s="56">
         <v>8830</v>
       </c>
-      <c r="B669" s="57" t="s">
-        <v>638</v>
+      <c r="B669" s="56" t="s">
+        <v>637</v>
       </c>
       <c r="C669" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A670" s="57">
+      <c r="A670" s="56">
         <v>8467</v>
       </c>
-      <c r="B670" s="57" t="s">
-        <v>639</v>
+      <c r="B670" s="56" t="s">
+        <v>638</v>
       </c>
       <c r="C670" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A671" s="57">
+      <c r="A671" s="56">
         <v>9482</v>
       </c>
-      <c r="B671" s="57" t="s">
-        <v>640</v>
+      <c r="B671" s="56" t="s">
+        <v>639</v>
       </c>
       <c r="C671" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A672" s="57">
+      <c r="A672" s="56">
         <v>8908</v>
       </c>
-      <c r="B672" s="57" t="s">
-        <v>641</v>
+      <c r="B672" s="56" t="s">
+        <v>640</v>
       </c>
       <c r="C672" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A673" s="57">
+      <c r="A673" s="56">
         <v>7231</v>
       </c>
-      <c r="B673" s="57" t="s">
-        <v>642</v>
+      <c r="B673" s="56" t="s">
+        <v>641</v>
       </c>
       <c r="C673" s="6" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A674" s="57">
+      <c r="A674" s="56">
         <v>8224</v>
       </c>
-      <c r="B674" s="57" t="s">
-        <v>643</v>
+      <c r="B674" s="56" t="s">
+        <v>642</v>
       </c>
       <c r="C674" s="6" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A675" s="57">
+      <c r="A675" s="56">
         <v>8204</v>
       </c>
-      <c r="B675" s="57" t="s">
-        <v>644</v>
+      <c r="B675" s="56" t="s">
+        <v>643</v>
       </c>
       <c r="C675" s="6" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A676" s="57">
+      <c r="A676" s="56">
         <v>8131</v>
       </c>
-      <c r="B676" s="57" t="s">
-        <v>645</v>
+      <c r="B676" s="56" t="s">
+        <v>644</v>
       </c>
       <c r="C676" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A677" s="57">
+      <c r="A677" s="56">
         <v>8855</v>
       </c>
-      <c r="B677" s="57" t="s">
-        <v>646</v>
+      <c r="B677" s="56" t="s">
+        <v>645</v>
       </c>
       <c r="C677" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A678" s="57">
+      <c r="A678" s="56">
         <v>9439</v>
       </c>
-      <c r="B678" s="57" t="s">
-        <v>647</v>
+      <c r="B678" s="56" t="s">
+        <v>646</v>
       </c>
       <c r="C678" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A679" s="57">
+      <c r="A679" s="56">
         <v>6601</v>
       </c>
-      <c r="B679" s="57" t="s">
-        <v>648</v>
+      <c r="B679" s="56" t="s">
+        <v>647</v>
       </c>
       <c r="C679" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A680" s="57">
+      <c r="A680" s="56">
         <v>7965</v>
       </c>
-      <c r="B680" s="57" t="s">
-        <v>649</v>
+      <c r="B680" s="56" t="s">
+        <v>648</v>
       </c>
       <c r="C680" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A681" s="57">
+      <c r="A681" s="56">
         <v>7716</v>
       </c>
-      <c r="B681" s="57" t="s">
-        <v>650</v>
+      <c r="B681" s="56" t="s">
+        <v>649</v>
       </c>
       <c r="C681" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A682" s="57">
+      <c r="A682" s="56">
         <v>9413</v>
       </c>
-      <c r="B682" s="57" t="s">
-        <v>651</v>
+      <c r="B682" s="56" t="s">
+        <v>650</v>
       </c>
       <c r="C682" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A683" s="57">
+      <c r="A683" s="56">
         <v>6395</v>
       </c>
-      <c r="B683" s="57" t="s">
-        <v>652</v>
+      <c r="B683" s="56" t="s">
+        <v>651</v>
       </c>
       <c r="C683" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A684" s="57">
+      <c r="A684" s="56">
         <v>6542</v>
       </c>
-      <c r="B684" s="57" t="s">
-        <v>653</v>
+      <c r="B684" s="56" t="s">
+        <v>652</v>
       </c>
       <c r="C684" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A685" s="57">
+      <c r="A685" s="56">
         <v>9151</v>
       </c>
-      <c r="B685" s="57" t="s">
-        <v>654</v>
+      <c r="B685" s="56" t="s">
+        <v>653</v>
       </c>
       <c r="C685" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A686" s="57">
+      <c r="A686" s="56">
         <v>6479</v>
       </c>
-      <c r="B686" s="57" t="s">
-        <v>655</v>
+      <c r="B686" s="56" t="s">
+        <v>654</v>
       </c>
       <c r="C686" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A687" s="57">
+      <c r="A687" s="56">
         <v>7925</v>
       </c>
-      <c r="B687" s="57" t="s">
+      <c r="B687" s="56" t="s">
         <v>68</v>
       </c>
       <c r="C687" s="6" t="s">
@@ -10779,219 +10802,219 @@
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A688" s="57">
+      <c r="A688" s="56">
         <v>6510</v>
       </c>
-      <c r="B688" s="57" t="s">
-        <v>656</v>
+      <c r="B688" s="56" t="s">
+        <v>655</v>
       </c>
       <c r="C688" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A689" s="57">
+      <c r="A689" s="56">
         <v>6420</v>
       </c>
-      <c r="B689" s="57" t="s">
-        <v>657</v>
+      <c r="B689" s="56" t="s">
+        <v>656</v>
       </c>
       <c r="C689" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A690" s="57">
+      <c r="A690" s="56">
         <v>6442</v>
       </c>
-      <c r="B690" s="57" t="s">
-        <v>658</v>
+      <c r="B690" s="56" t="s">
+        <v>657</v>
       </c>
       <c r="C690" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A691" s="57">
+      <c r="A691" s="56">
         <v>6423</v>
       </c>
-      <c r="B691" s="57" t="s">
-        <v>659</v>
+      <c r="B691" s="56" t="s">
+        <v>658</v>
       </c>
       <c r="C691" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A692" s="57">
+      <c r="A692" s="56">
         <v>9477</v>
       </c>
-      <c r="B692" s="57" t="s">
-        <v>660</v>
+      <c r="B692" s="56" t="s">
+        <v>659</v>
       </c>
       <c r="C692" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A693" s="57">
+      <c r="A693" s="56">
         <v>7442</v>
       </c>
-      <c r="B693" s="57" t="s">
-        <v>661</v>
+      <c r="B693" s="56" t="s">
+        <v>660</v>
       </c>
       <c r="C693" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A694" s="57">
+      <c r="A694" s="56">
         <v>8443</v>
       </c>
-      <c r="B694" s="57" t="s">
-        <v>662</v>
+      <c r="B694" s="56" t="s">
+        <v>661</v>
       </c>
       <c r="C694" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A695" s="57">
+      <c r="A695" s="56">
         <v>7193</v>
       </c>
-      <c r="B695" s="57" t="s">
-        <v>663</v>
+      <c r="B695" s="56" t="s">
+        <v>662</v>
       </c>
       <c r="C695" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A696" s="57">
+      <c r="A696" s="56">
         <v>6749</v>
       </c>
-      <c r="B696" s="57" t="s">
-        <v>652</v>
+      <c r="B696" s="56" t="s">
+        <v>651</v>
       </c>
       <c r="C696" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A697" s="57">
+      <c r="A697" s="56">
         <v>6406</v>
       </c>
-      <c r="B697" s="57" t="s">
-        <v>664</v>
+      <c r="B697" s="56" t="s">
+        <v>663</v>
       </c>
       <c r="C697" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A698" s="57">
+      <c r="A698" s="56">
         <v>6379</v>
       </c>
-      <c r="B698" s="57" t="s">
-        <v>665</v>
+      <c r="B698" s="56" t="s">
+        <v>664</v>
       </c>
       <c r="C698" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A699" s="57">
+      <c r="A699" s="56">
         <v>8274</v>
       </c>
-      <c r="B699" s="57" t="s">
-        <v>666</v>
+      <c r="B699" s="56" t="s">
+        <v>665</v>
       </c>
       <c r="C699" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A700" s="57">
+      <c r="A700" s="56">
         <v>7532</v>
       </c>
-      <c r="B700" s="57" t="s">
-        <v>667</v>
+      <c r="B700" s="56" t="s">
+        <v>666</v>
       </c>
       <c r="C700" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A701" s="57">
+      <c r="A701" s="56">
         <v>8047</v>
       </c>
-      <c r="B701" s="57" t="s">
-        <v>668</v>
+      <c r="B701" s="56" t="s">
+        <v>667</v>
       </c>
       <c r="C701" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A702" s="57">
+      <c r="A702" s="56">
         <v>7700</v>
       </c>
-      <c r="B702" s="57" t="s">
-        <v>669</v>
+      <c r="B702" s="56" t="s">
+        <v>668</v>
       </c>
       <c r="C702" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A703" s="57">
+      <c r="A703" s="56">
         <v>9449</v>
       </c>
-      <c r="B703" s="57" t="s">
-        <v>646</v>
+      <c r="B703" s="56" t="s">
+        <v>645</v>
       </c>
       <c r="C703" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A704" s="57">
+      <c r="A704" s="56">
         <v>6170</v>
       </c>
-      <c r="B704" s="57" t="s">
-        <v>670</v>
+      <c r="B704" s="56" t="s">
+        <v>669</v>
       </c>
       <c r="C704" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A705" s="57">
+      <c r="A705" s="56">
         <v>6174</v>
       </c>
-      <c r="B705" s="57" t="s">
-        <v>671</v>
+      <c r="B705" s="56" t="s">
+        <v>670</v>
       </c>
       <c r="C705" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A706" s="57">
+      <c r="A706" s="56">
         <v>9581</v>
       </c>
-      <c r="B706" s="57" t="s">
-        <v>672</v>
+      <c r="B706" s="56" t="s">
+        <v>671</v>
       </c>
       <c r="C706" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A707" s="57">
+      <c r="A707" s="56">
         <v>7365</v>
       </c>
-      <c r="B707" s="57" t="s">
+      <c r="B707" s="56" t="s">
         <v>104</v>
       </c>
       <c r="C707" s="6" t="s">
@@ -10999,32 +11022,32 @@
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A708" s="57">
+      <c r="A708" s="56">
         <v>6875</v>
       </c>
-      <c r="B708" s="57" t="s">
-        <v>673</v>
+      <c r="B708" s="56" t="s">
+        <v>672</v>
       </c>
       <c r="C708" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A709" s="57">
+      <c r="A709" s="56">
         <v>6463</v>
       </c>
-      <c r="B709" s="57" t="s">
-        <v>674</v>
+      <c r="B709" s="56" t="s">
+        <v>673</v>
       </c>
       <c r="C709" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A710" s="57">
+      <c r="A710" s="56">
         <v>6145</v>
       </c>
-      <c r="B710" s="57" t="s">
+      <c r="B710" s="56" t="s">
         <v>105</v>
       </c>
       <c r="C710" s="6" t="s">
@@ -11032,10 +11055,10 @@
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A711" s="57">
+      <c r="A711" s="56">
         <v>8102</v>
       </c>
-      <c r="B711" s="57" t="s">
+      <c r="B711" s="56" t="s">
         <v>115</v>
       </c>
       <c r="C711" s="6" t="s">
@@ -11043,21 +11066,21 @@
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A712" s="57">
+      <c r="A712" s="56">
         <v>6343</v>
       </c>
-      <c r="B712" s="57" t="s">
-        <v>675</v>
+      <c r="B712" s="56" t="s">
+        <v>674</v>
       </c>
       <c r="C712" s="6" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A713" s="57">
+      <c r="A713" s="56">
         <v>7824</v>
       </c>
-      <c r="B713" s="57" t="s">
+      <c r="B713" s="56" t="s">
         <v>131</v>
       </c>
       <c r="C713" s="6" t="s">
@@ -11065,10 +11088,10 @@
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A714" s="57">
+      <c r="A714" s="56">
         <v>6980</v>
       </c>
-      <c r="B714" s="57" t="s">
+      <c r="B714" s="56" t="s">
         <v>361</v>
       </c>
       <c r="C714" s="6" t="s">
@@ -11076,21 +11099,21 @@
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A715" s="57">
+      <c r="A715" s="56">
         <v>5899</v>
       </c>
-      <c r="B715" s="57" t="s">
-        <v>676</v>
+      <c r="B715" s="56" t="s">
+        <v>675</v>
       </c>
       <c r="C715" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A716" s="57">
+      <c r="A716" s="56">
         <v>8139</v>
       </c>
-      <c r="B716" s="57" t="s">
+      <c r="B716" s="56" t="s">
         <v>133</v>
       </c>
       <c r="C716" s="6" t="s">
@@ -11098,32 +11121,32 @@
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A717" s="57">
+      <c r="A717" s="56">
         <v>6921</v>
       </c>
-      <c r="B717" s="57" t="s">
-        <v>677</v>
+      <c r="B717" s="56" t="s">
+        <v>676</v>
       </c>
       <c r="C717" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A718" s="57">
+      <c r="A718" s="56">
         <v>8638</v>
       </c>
-      <c r="B718" s="57" t="s">
-        <v>678</v>
+      <c r="B718" s="56" t="s">
+        <v>677</v>
       </c>
       <c r="C718" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A719" s="57">
+      <c r="A719" s="56">
         <v>6960</v>
       </c>
-      <c r="B719" s="57" t="s">
+      <c r="B719" s="56" t="s">
         <v>129</v>
       </c>
       <c r="C719" s="6" t="s">
@@ -11131,10 +11154,10 @@
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A720" s="57">
+      <c r="A720" s="56">
         <v>5933</v>
       </c>
-      <c r="B720" s="57" t="s">
+      <c r="B720" s="56" t="s">
         <v>130</v>
       </c>
       <c r="C720" s="6" t="s">
@@ -11142,10 +11165,10 @@
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A721" s="57">
+      <c r="A721" s="56">
         <v>5854</v>
       </c>
-      <c r="B721" s="57" t="s">
+      <c r="B721" s="56" t="s">
         <v>132</v>
       </c>
       <c r="C721" s="6" t="s">
@@ -11153,10 +11176,10 @@
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A722" s="57">
+      <c r="A722" s="56">
         <v>6401</v>
       </c>
-      <c r="B722" s="57" t="s">
+      <c r="B722" s="56" t="s">
         <v>552</v>
       </c>
       <c r="C722" s="6" t="s">
@@ -11164,10 +11187,10 @@
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A723" s="57">
+      <c r="A723" s="56">
         <v>5913</v>
       </c>
-      <c r="B723" s="57" t="s">
+      <c r="B723" s="56" t="s">
         <v>123</v>
       </c>
       <c r="C723" s="6" t="s">
@@ -11175,32 +11198,32 @@
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A724" s="57">
+      <c r="A724" s="56">
         <v>5850</v>
       </c>
-      <c r="B724" s="57" t="s">
-        <v>679</v>
+      <c r="B724" s="56" t="s">
+        <v>678</v>
       </c>
       <c r="C724" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A725" s="57">
+      <c r="A725" s="56">
         <v>6484</v>
       </c>
-      <c r="B725" s="57" t="s">
-        <v>680</v>
+      <c r="B725" s="56" t="s">
+        <v>679</v>
       </c>
       <c r="C725" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A726" s="57">
+      <c r="A726" s="56">
         <v>5866</v>
       </c>
-      <c r="B726" s="57" t="s">
+      <c r="B726" s="56" t="s">
         <v>377</v>
       </c>
       <c r="C726" s="6" t="s">
@@ -11208,65 +11231,65 @@
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A727" s="57">
+      <c r="A727" s="56">
         <v>5841</v>
       </c>
-      <c r="B727" s="57" t="s">
-        <v>681</v>
+      <c r="B727" s="56" t="s">
+        <v>680</v>
       </c>
       <c r="C727" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A728" s="57">
+      <c r="A728" s="56">
         <v>7962</v>
       </c>
-      <c r="B728" s="57" t="s">
-        <v>682</v>
+      <c r="B728" s="56" t="s">
+        <v>681</v>
       </c>
       <c r="C728" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A729" s="57">
+      <c r="A729" s="56">
         <v>8918</v>
       </c>
-      <c r="B729" s="57" t="s">
-        <v>683</v>
+      <c r="B729" s="56" t="s">
+        <v>682</v>
       </c>
       <c r="C729" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A730" s="57">
+      <c r="A730" s="56">
         <v>6572</v>
       </c>
-      <c r="B730" s="57" t="s">
-        <v>684</v>
+      <c r="B730" s="56" t="s">
+        <v>683</v>
       </c>
       <c r="C730" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A731" s="57">
+      <c r="A731" s="56">
         <v>5857</v>
       </c>
-      <c r="B731" s="57" t="s">
-        <v>685</v>
+      <c r="B731" s="56" t="s">
+        <v>684</v>
       </c>
       <c r="C731" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A732" s="57">
+      <c r="A732" s="56">
         <v>5849</v>
       </c>
-      <c r="B732" s="57" t="s">
+      <c r="B732" s="56" t="s">
         <v>550</v>
       </c>
       <c r="C732" s="6" t="s">
@@ -11274,21 +11297,21 @@
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A733" s="57">
+      <c r="A733" s="56">
         <v>6789</v>
       </c>
-      <c r="B733" s="57" t="s">
-        <v>686</v>
+      <c r="B733" s="56" t="s">
+        <v>685</v>
       </c>
       <c r="C733" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A734" s="57">
+      <c r="A734" s="56">
         <v>6925</v>
       </c>
-      <c r="B734" s="57" t="s">
+      <c r="B734" s="56" t="s">
         <v>55</v>
       </c>
       <c r="C734" s="6" t="s">
@@ -11296,10 +11319,10 @@
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A735" s="57">
+      <c r="A735" s="56">
         <v>5902</v>
       </c>
-      <c r="B735" s="57" t="s">
+      <c r="B735" s="56" t="s">
         <v>138</v>
       </c>
       <c r="C735" s="6" t="s">
@@ -11307,76 +11330,76 @@
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A736" s="57">
+      <c r="A736" s="56">
         <v>8824</v>
       </c>
-      <c r="B736" s="57" t="s">
-        <v>687</v>
+      <c r="B736" s="56" t="s">
+        <v>686</v>
       </c>
       <c r="C736" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A737" s="57">
+      <c r="A737" s="56">
         <v>5898</v>
       </c>
-      <c r="B737" s="57" t="s">
-        <v>688</v>
+      <c r="B737" s="56" t="s">
+        <v>687</v>
       </c>
       <c r="C737" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A738" s="57">
+      <c r="A738" s="56">
         <v>8826</v>
       </c>
-      <c r="B738" s="57" t="s">
-        <v>689</v>
+      <c r="B738" s="56" t="s">
+        <v>688</v>
       </c>
       <c r="C738" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A739" s="57">
+      <c r="A739" s="56">
         <v>8478</v>
       </c>
-      <c r="B739" s="57" t="s">
-        <v>690</v>
+      <c r="B739" s="56" t="s">
+        <v>689</v>
       </c>
       <c r="C739" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A740" s="57">
+      <c r="A740" s="56">
         <v>5937</v>
       </c>
-      <c r="B740" s="57" t="s">
-        <v>691</v>
+      <c r="B740" s="56" t="s">
+        <v>690</v>
       </c>
       <c r="C740" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A741" s="57">
+      <c r="A741" s="56">
         <v>5916</v>
       </c>
-      <c r="B741" s="57" t="s">
-        <v>692</v>
+      <c r="B741" s="56" t="s">
+        <v>691</v>
       </c>
       <c r="C741" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A742" s="57">
+      <c r="A742" s="56">
         <v>6806</v>
       </c>
-      <c r="B742" s="57" t="s">
+      <c r="B742" s="56" t="s">
         <v>137</v>
       </c>
       <c r="C742" s="6" t="s">
@@ -11384,65 +11407,65 @@
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A743" s="57">
+      <c r="A743" s="56">
         <v>5882</v>
       </c>
-      <c r="B743" s="57" t="s">
-        <v>693</v>
+      <c r="B743" s="56" t="s">
+        <v>692</v>
       </c>
       <c r="C743" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A744" s="57">
+      <c r="A744" s="56">
         <v>5958</v>
       </c>
-      <c r="B744" s="57" t="s">
-        <v>694</v>
+      <c r="B744" s="56" t="s">
+        <v>693</v>
       </c>
       <c r="C744" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A745" s="57">
+      <c r="A745" s="56">
         <v>9244</v>
       </c>
-      <c r="B745" s="57" t="s">
-        <v>695</v>
+      <c r="B745" s="56" t="s">
+        <v>694</v>
       </c>
       <c r="C745" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A746" s="57">
+      <c r="A746" s="56">
         <v>6662</v>
       </c>
-      <c r="B746" s="57" t="s">
-        <v>696</v>
+      <c r="B746" s="56" t="s">
+        <v>695</v>
       </c>
       <c r="C746" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A747" s="57">
+      <c r="A747" s="56">
         <v>8369</v>
       </c>
-      <c r="B747" s="57" t="s">
-        <v>697</v>
+      <c r="B747" s="56" t="s">
+        <v>696</v>
       </c>
       <c r="C747" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A748" s="57">
+      <c r="A748" s="56">
         <v>5894</v>
       </c>
-      <c r="B748" s="57" t="s">
+      <c r="B748" s="56" t="s">
         <v>139</v>
       </c>
       <c r="C748" s="6" t="s">
@@ -11450,735 +11473,743 @@
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A749" s="73">
+      <c r="A749" s="71">
         <v>6009</v>
       </c>
-      <c r="B749" s="73" t="s">
+      <c r="B749" s="71" t="s">
+        <v>697</v>
+      </c>
+      <c r="C749" s="72" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A750" s="71">
+        <v>5845</v>
+      </c>
+      <c r="B750" s="71" t="s">
         <v>698</v>
       </c>
-      <c r="C749" s="74" t="s">
+      <c r="C750" s="72" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A750" s="73">
-        <v>5845</v>
-      </c>
-      <c r="B750" s="73" t="s">
+    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A751" s="71">
+        <v>5840</v>
+      </c>
+      <c r="B751" s="71" t="s">
         <v>699</v>
       </c>
-      <c r="C750" s="74" t="s">
+      <c r="C751" s="72" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A751" s="73">
-        <v>5840</v>
-      </c>
-      <c r="B751" s="73" t="s">
+    <row r="752" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A752" s="71">
+        <v>5989</v>
+      </c>
+      <c r="B752" s="71" t="s">
         <v>700</v>
       </c>
-      <c r="C751" s="74" t="s">
+      <c r="C752" s="72" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="752" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A752" s="73">
-        <v>5989</v>
-      </c>
-      <c r="B752" s="73" t="s">
+    <row r="753" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A753" s="85">
+        <v>5528</v>
+      </c>
+      <c r="B753" s="73" t="s">
         <v>701</v>
       </c>
-      <c r="C752" s="74" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="753" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A753" s="75">
-        <v>5528</v>
-      </c>
-      <c r="B753" s="76" t="s">
+      <c r="C753" s="73" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A754" s="86">
+        <v>7580</v>
+      </c>
+      <c r="B754" s="74" t="s">
         <v>702</v>
       </c>
-      <c r="C753" s="76" t="s">
+      <c r="C754" s="74" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="754" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A754" s="77">
-        <v>7580</v>
-      </c>
-      <c r="B754" s="78" t="s">
+    <row r="755" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A755" s="87">
+        <v>4867</v>
+      </c>
+      <c r="B755" s="75" t="s">
         <v>703</v>
       </c>
-      <c r="C754" s="78" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="755" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A755" s="79">
-        <v>4867</v>
-      </c>
-      <c r="B755" s="80" t="s">
+      <c r="C755" s="75" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A756" s="87">
+        <v>7767</v>
+      </c>
+      <c r="B756" s="75" t="s">
         <v>704</v>
       </c>
-      <c r="C755" s="80" t="s">
+      <c r="C756" s="75" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="756" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A756" s="79">
-        <v>7767</v>
-      </c>
-      <c r="B756" s="80" t="s">
+    <row r="757" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A757" s="88">
+        <v>7928</v>
+      </c>
+      <c r="B757" s="70" t="s">
+        <v>520</v>
+      </c>
+      <c r="C757" s="79" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A758" s="89">
+        <v>6187</v>
+      </c>
+      <c r="B758" s="76" t="s">
         <v>705</v>
-      </c>
-      <c r="C756" s="80" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="757" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A757" s="71">
-        <v>7928</v>
-      </c>
-      <c r="B757" s="72" t="s">
-        <v>520</v>
-      </c>
-      <c r="C757" s="86" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="758" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A758" s="81">
-        <v>6187</v>
-      </c>
-      <c r="B758" s="83" t="s">
-        <v>706</v>
       </c>
       <c r="C758" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="759" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A759" s="82">
+      <c r="A759" s="90">
         <v>6249</v>
       </c>
-      <c r="B759" s="84" t="s">
-        <v>707</v>
+      <c r="B759" s="77" t="s">
+        <v>706</v>
       </c>
       <c r="C759" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="760" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A760" s="82">
+      <c r="A760" s="90">
         <v>6180</v>
       </c>
-      <c r="B760" s="84" t="s">
-        <v>708</v>
+      <c r="B760" s="77" t="s">
+        <v>722</v>
       </c>
       <c r="C760" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="761" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A761" s="82">
+      <c r="A761" s="90">
         <v>6242</v>
       </c>
-      <c r="B761" s="85" t="s">
-        <v>709</v>
+      <c r="B761" s="78" t="s">
+        <v>723</v>
       </c>
       <c r="C761" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="762" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A762" s="82">
+      <c r="A762" s="90">
         <v>6788</v>
       </c>
-      <c r="B762" s="85" t="s">
-        <v>710</v>
+      <c r="B762" s="78" t="s">
+        <v>707</v>
       </c>
       <c r="C762" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="763" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A763" s="82">
+      <c r="A763" s="90">
         <v>8254</v>
       </c>
-      <c r="B763" s="85" t="s">
-        <v>711</v>
+      <c r="B763" s="78" t="s">
+        <v>708</v>
       </c>
       <c r="C763" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="764" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A764" s="82">
+      <c r="A764" s="90">
         <v>8468</v>
       </c>
-      <c r="B764" s="85" t="s">
-        <v>712</v>
+      <c r="B764" s="78" t="s">
+        <v>709</v>
       </c>
       <c r="C764" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="765" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A765" s="82">
+      <c r="A765" s="90">
         <v>8624</v>
       </c>
-      <c r="B765" s="85" t="s">
-        <v>713</v>
+      <c r="B765" s="78" t="s">
+        <v>710</v>
       </c>
       <c r="C765" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="766" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A766" s="82">
+      <c r="A766" s="90">
         <v>7298</v>
       </c>
-      <c r="B766" s="85" t="s">
-        <v>714</v>
+      <c r="B766" s="78" t="s">
+        <v>711</v>
       </c>
       <c r="C766" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="767" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A767" s="82">
+      <c r="A767" s="90">
         <v>6333</v>
       </c>
-      <c r="B767" s="85" t="s">
-        <v>715</v>
+      <c r="B767" s="78" t="s">
+        <v>712</v>
       </c>
       <c r="C767" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="768" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A768" s="82">
+      <c r="A768" s="90">
         <v>8713</v>
       </c>
-      <c r="B768" s="85" t="s">
-        <v>716</v>
+      <c r="B768" s="78" t="s">
+        <v>713</v>
       </c>
       <c r="C768" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="769" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A769" s="82">
+      <c r="A769" s="90">
         <v>8600</v>
       </c>
-      <c r="B769" s="85" t="s">
-        <v>717</v>
+      <c r="B769" s="78" t="s">
+        <v>714</v>
       </c>
       <c r="C769" s="6" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="770" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A770" s="82">
+    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A770" s="91">
         <v>9209</v>
       </c>
-      <c r="B770" s="85" t="s">
+      <c r="B770" s="80" t="s">
+        <v>715</v>
+      </c>
+      <c r="C770" s="66" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A771" s="81">
+        <v>6160</v>
+      </c>
+      <c r="B771" s="81" t="s">
+        <v>716</v>
+      </c>
+      <c r="C771" s="56" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A772" s="81">
+        <v>6968</v>
+      </c>
+      <c r="B772" s="81" t="s">
+        <v>717</v>
+      </c>
+      <c r="C772" s="56" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A773" s="81">
+        <v>8574</v>
+      </c>
+      <c r="B773" s="81" t="s">
         <v>718</v>
       </c>
-      <c r="C770" s="6" t="s">
+      <c r="C773" s="56" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="771" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A771" s="82">
-        <v>6160</v>
-      </c>
-      <c r="B771" s="85" t="s">
+    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A774" s="81">
+        <v>6892</v>
+      </c>
+      <c r="B774" s="81" t="s">
         <v>719</v>
       </c>
-      <c r="C771" s="6" t="s">
+      <c r="C774" s="56" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="772" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A772" s="82">
-        <v>6968</v>
-      </c>
-      <c r="B772" s="85" t="s">
+    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A775" s="81">
+        <v>8276</v>
+      </c>
+      <c r="B775" s="81" t="s">
         <v>720</v>
       </c>
-      <c r="C772" s="6" t="s">
+      <c r="C775" s="56" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="773" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A773" s="82">
-        <v>8574</v>
-      </c>
-      <c r="B773" s="85" t="s">
+    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A776" s="81">
+        <v>9029</v>
+      </c>
+      <c r="B776" s="81" t="s">
         <v>721</v>
       </c>
-      <c r="C773" s="6" t="s">
+      <c r="C776" s="56" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="774" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A774" s="82">
-        <v>6892</v>
-      </c>
-      <c r="B774" s="85" t="s">
-        <v>722</v>
-      </c>
-      <c r="C774" s="6" t="s">
+    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A777" s="69">
+        <v>9179</v>
+      </c>
+      <c r="B777" s="82" t="s">
+        <v>724</v>
+      </c>
+      <c r="C777" s="83" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="775" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A775" s="82">
-        <v>8276</v>
-      </c>
-      <c r="B775" s="85" t="s">
-        <v>723</v>
-      </c>
-      <c r="C775" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="776" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A776" s="82">
-        <v>9029</v>
-      </c>
-      <c r="B776" s="85" t="s">
-        <v>724</v>
-      </c>
-      <c r="C776" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C777" s="54"/>
-    </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C778" s="54"/>
+      <c r="C778" s="53"/>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C779" s="54"/>
+      <c r="C779" s="53"/>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C780" s="54"/>
+      <c r="C780" s="53"/>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C781" s="54"/>
+      <c r="C781" s="53"/>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C782" s="54"/>
+      <c r="C782" s="53"/>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C783" s="54"/>
+      <c r="C783" s="53"/>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C784" s="54"/>
+      <c r="C784" s="53"/>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C785" s="54"/>
+      <c r="C785" s="53"/>
     </row>
     <row r="786" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C786" s="54"/>
+      <c r="C786" s="53"/>
     </row>
     <row r="787" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C787" s="54"/>
+      <c r="C787" s="53"/>
     </row>
     <row r="788" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C788" s="54"/>
+      <c r="C788" s="53"/>
     </row>
     <row r="789" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C789" s="54"/>
+      <c r="C789" s="53"/>
     </row>
     <row r="790" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C790" s="54"/>
+      <c r="C790" s="53"/>
     </row>
     <row r="791" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C791" s="54"/>
+      <c r="C791" s="53"/>
     </row>
     <row r="792" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C792" s="54"/>
+      <c r="C792" s="53"/>
     </row>
     <row r="793" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C793" s="54"/>
+      <c r="C793" s="53"/>
     </row>
     <row r="794" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C794" s="54"/>
+      <c r="C794" s="53"/>
     </row>
     <row r="795" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C795" s="54"/>
+      <c r="C795" s="53"/>
     </row>
     <row r="796" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C796" s="54"/>
+      <c r="C796" s="53"/>
     </row>
     <row r="797" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C797" s="54"/>
+      <c r="C797" s="53"/>
     </row>
     <row r="798" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C798" s="54"/>
+      <c r="C798" s="53"/>
     </row>
     <row r="799" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C799" s="54"/>
+      <c r="C799" s="53"/>
     </row>
     <row r="800" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C800" s="54"/>
+      <c r="C800" s="53"/>
     </row>
     <row r="801" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C801" s="54"/>
+      <c r="C801" s="53"/>
     </row>
     <row r="802" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C802" s="54"/>
+      <c r="C802" s="53"/>
     </row>
     <row r="803" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C803" s="54"/>
+      <c r="C803" s="53"/>
     </row>
     <row r="804" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C804" s="54"/>
+      <c r="C804" s="53"/>
     </row>
     <row r="805" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C805" s="54"/>
+      <c r="C805" s="53"/>
     </row>
     <row r="806" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C806" s="54"/>
+      <c r="C806" s="53"/>
     </row>
     <row r="807" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C807" s="54"/>
+      <c r="C807" s="53"/>
     </row>
     <row r="808" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C808" s="54"/>
+      <c r="C808" s="53"/>
     </row>
     <row r="809" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C809" s="54"/>
+      <c r="C809" s="53"/>
     </row>
     <row r="810" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C810" s="54"/>
+      <c r="C810" s="53"/>
     </row>
     <row r="811" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C811" s="54"/>
+      <c r="C811" s="53"/>
     </row>
     <row r="812" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C812" s="54"/>
+      <c r="C812" s="53"/>
     </row>
     <row r="813" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C813" s="54"/>
+      <c r="C813" s="53"/>
     </row>
     <row r="814" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C814" s="54"/>
+      <c r="C814" s="53"/>
     </row>
     <row r="815" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C815" s="54"/>
+      <c r="C815" s="53"/>
     </row>
     <row r="816" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C816" s="54"/>
+      <c r="C816" s="53"/>
     </row>
     <row r="817" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C817" s="54"/>
+      <c r="C817" s="53"/>
     </row>
     <row r="818" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C818" s="54"/>
+      <c r="C818" s="53"/>
     </row>
     <row r="819" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C819" s="54"/>
+      <c r="C819" s="53"/>
     </row>
     <row r="820" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C820" s="54"/>
+      <c r="C820" s="53"/>
     </row>
     <row r="821" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C821" s="54"/>
+      <c r="C821" s="53"/>
     </row>
     <row r="822" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C822" s="54"/>
+      <c r="C822" s="53"/>
     </row>
     <row r="823" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C823" s="54"/>
+      <c r="C823" s="53"/>
     </row>
     <row r="824" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C824" s="54"/>
+      <c r="C824" s="53"/>
     </row>
     <row r="825" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C825" s="54"/>
+      <c r="C825" s="53"/>
     </row>
     <row r="826" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C826" s="54"/>
+      <c r="C826" s="53"/>
     </row>
     <row r="827" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C827" s="54"/>
+      <c r="C827" s="53"/>
     </row>
     <row r="828" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C828" s="54"/>
+      <c r="C828" s="53"/>
     </row>
     <row r="829" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C829" s="54"/>
+      <c r="C829" s="53"/>
     </row>
     <row r="830" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C830" s="54"/>
+      <c r="C830" s="53"/>
     </row>
     <row r="831" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C831" s="54"/>
+      <c r="C831" s="53"/>
     </row>
     <row r="832" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C832" s="54"/>
+      <c r="C832" s="53"/>
     </row>
     <row r="833" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C833" s="54"/>
+      <c r="C833" s="53"/>
     </row>
     <row r="834" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C834" s="54"/>
+      <c r="C834" s="53"/>
     </row>
     <row r="835" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C835" s="54"/>
+      <c r="C835" s="53"/>
     </row>
     <row r="836" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C836" s="54"/>
+      <c r="C836" s="53"/>
     </row>
     <row r="837" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C837" s="54"/>
+      <c r="C837" s="53"/>
     </row>
     <row r="838" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C838" s="54"/>
+      <c r="C838" s="53"/>
     </row>
     <row r="839" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C839" s="54"/>
+      <c r="C839" s="53"/>
     </row>
     <row r="840" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C840" s="54"/>
+      <c r="C840" s="53"/>
     </row>
     <row r="841" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C841" s="54"/>
+      <c r="C841" s="53"/>
     </row>
     <row r="842" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C842" s="54"/>
+      <c r="C842" s="53"/>
     </row>
     <row r="843" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C843" s="54"/>
+      <c r="C843" s="53"/>
     </row>
     <row r="844" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C844" s="54"/>
+      <c r="C844" s="53"/>
     </row>
     <row r="845" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C845" s="54"/>
+      <c r="C845" s="53"/>
     </row>
     <row r="846" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C846" s="54"/>
+      <c r="C846" s="53"/>
     </row>
     <row r="847" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C847" s="54"/>
+      <c r="C847" s="53"/>
     </row>
     <row r="848" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C848" s="54"/>
+      <c r="C848" s="53"/>
     </row>
     <row r="849" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C849" s="54"/>
+      <c r="C849" s="53"/>
     </row>
     <row r="850" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C850" s="54"/>
+      <c r="C850" s="53"/>
     </row>
     <row r="851" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C851" s="54"/>
+      <c r="C851" s="53"/>
     </row>
     <row r="852" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C852" s="54"/>
+      <c r="C852" s="53"/>
     </row>
     <row r="853" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C853" s="54"/>
+      <c r="C853" s="53"/>
     </row>
     <row r="854" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C854" s="54"/>
+      <c r="C854" s="53"/>
     </row>
     <row r="855" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C855" s="54"/>
+      <c r="C855" s="53"/>
     </row>
     <row r="856" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C856" s="54"/>
+      <c r="C856" s="53"/>
     </row>
     <row r="857" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C857" s="54"/>
+      <c r="C857" s="53"/>
     </row>
     <row r="858" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C858" s="54"/>
+      <c r="C858" s="53"/>
     </row>
     <row r="859" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C859" s="54"/>
+      <c r="C859" s="53"/>
     </row>
     <row r="860" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C860" s="54"/>
+      <c r="C860" s="53"/>
     </row>
     <row r="861" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C861" s="54"/>
+      <c r="C861" s="53"/>
     </row>
     <row r="862" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C862" s="54"/>
+      <c r="C862" s="53"/>
     </row>
     <row r="863" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C863" s="54"/>
+      <c r="C863" s="53"/>
     </row>
     <row r="864" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C864" s="54"/>
+      <c r="C864" s="53"/>
     </row>
     <row r="865" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C865" s="54"/>
+      <c r="C865" s="53"/>
     </row>
     <row r="866" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C866" s="54"/>
+      <c r="C866" s="53"/>
     </row>
     <row r="867" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C867" s="54"/>
+      <c r="C867" s="53"/>
     </row>
     <row r="868" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C868" s="54"/>
+      <c r="C868" s="53"/>
     </row>
     <row r="869" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C869" s="54"/>
+      <c r="C869" s="53"/>
     </row>
     <row r="870" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C870" s="54"/>
+      <c r="C870" s="53"/>
     </row>
     <row r="871" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C871" s="54"/>
+      <c r="C871" s="53"/>
     </row>
     <row r="872" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C872" s="54"/>
+      <c r="C872" s="53"/>
     </row>
     <row r="873" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C873" s="54"/>
+      <c r="C873" s="53"/>
     </row>
     <row r="874" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C874" s="54"/>
+      <c r="C874" s="53"/>
     </row>
     <row r="875" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C875" s="54"/>
+      <c r="C875" s="53"/>
     </row>
     <row r="876" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C876" s="54"/>
+      <c r="C876" s="53"/>
     </row>
     <row r="877" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C877" s="54"/>
+      <c r="C877" s="53"/>
     </row>
     <row r="878" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C878" s="54"/>
+      <c r="C878" s="53"/>
     </row>
     <row r="879" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C879" s="54"/>
+      <c r="C879" s="53"/>
     </row>
     <row r="880" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C880" s="54"/>
+      <c r="C880" s="53"/>
     </row>
     <row r="881" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C881" s="54"/>
+      <c r="C881" s="53"/>
     </row>
     <row r="882" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C882" s="54"/>
+      <c r="C882" s="53"/>
     </row>
     <row r="883" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C883" s="54"/>
+      <c r="C883" s="53"/>
     </row>
     <row r="884" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C884" s="54"/>
+      <c r="C884" s="53"/>
     </row>
     <row r="885" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C885" s="54"/>
+      <c r="C885" s="53"/>
     </row>
     <row r="886" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C886" s="54"/>
+      <c r="C886" s="53"/>
     </row>
     <row r="887" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C887" s="54"/>
+      <c r="C887" s="53"/>
     </row>
     <row r="888" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C888" s="54"/>
+      <c r="C888" s="53"/>
     </row>
     <row r="889" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C889" s="54"/>
+      <c r="C889" s="53"/>
     </row>
     <row r="890" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C890" s="54"/>
+      <c r="C890" s="53"/>
     </row>
     <row r="891" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C891" s="54"/>
+      <c r="C891" s="53"/>
     </row>
     <row r="892" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C892" s="54"/>
+      <c r="C892" s="53"/>
     </row>
     <row r="893" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C893" s="54"/>
+      <c r="C893" s="53"/>
     </row>
     <row r="894" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C894" s="54"/>
+      <c r="C894" s="53"/>
     </row>
     <row r="895" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C895" s="54"/>
+      <c r="C895" s="53"/>
     </row>
     <row r="896" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C896" s="54"/>
+      <c r="C896" s="53"/>
     </row>
     <row r="897" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C897" s="54"/>
+      <c r="C897" s="53"/>
     </row>
     <row r="898" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C898" s="54"/>
+      <c r="C898" s="53"/>
     </row>
     <row r="899" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C899" s="54"/>
+      <c r="C899" s="53"/>
     </row>
     <row r="900" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C900" s="54"/>
+      <c r="C900" s="53"/>
     </row>
     <row r="901" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C901" s="54"/>
+      <c r="C901" s="53"/>
     </row>
     <row r="902" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C902" s="54"/>
+      <c r="C902" s="53"/>
     </row>
     <row r="903" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C903" s="54"/>
+      <c r="C903" s="53"/>
     </row>
     <row r="904" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C904" s="54"/>
+      <c r="C904" s="53"/>
     </row>
     <row r="905" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C905" s="54"/>
+      <c r="C905" s="53"/>
     </row>
     <row r="906" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C906" s="54"/>
+      <c r="C906" s="53"/>
     </row>
     <row r="907" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C907" s="54"/>
+      <c r="C907" s="53"/>
     </row>
     <row r="908" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C908" s="54"/>
+      <c r="C908" s="53"/>
     </row>
     <row r="909" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C909" s="54"/>
+      <c r="C909" s="53"/>
     </row>
     <row r="910" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C910" s="54"/>
+      <c r="C910" s="53"/>
     </row>
     <row r="911" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C911" s="54"/>
+      <c r="C911" s="53"/>
     </row>
     <row r="912" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C912" s="54"/>
+      <c r="C912" s="53"/>
     </row>
     <row r="913" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C913" s="54"/>
+      <c r="C913" s="53"/>
     </row>
     <row r="914" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C914" s="54"/>
+      <c r="C914" s="53"/>
     </row>
     <row r="915" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C915" s="54"/>
+      <c r="C915" s="53"/>
     </row>
     <row r="916" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C916" s="54"/>
+      <c r="C916" s="53"/>
     </row>
     <row r="917" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C917" s="53"/>
+      <c r="C917" s="52"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/winners.xlsx
+++ b/winners.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="725">
   <si>
     <t>Admission_Number</t>
   </si>
@@ -1683,9 +1683,6 @@
   </si>
   <si>
     <t>BHAVYA</t>
-  </si>
-  <si>
-    <t>DIYA SAINI</t>
   </si>
   <si>
     <t>GARVPREET SINGH GILL</t>
@@ -5903,7 +5900,7 @@
         <v>222</v>
       </c>
       <c r="J242" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -9486,10 +9483,10 @@
         <v>9089</v>
       </c>
       <c r="B568" s="50" t="s">
-        <v>553</v>
+        <v>304</v>
       </c>
       <c r="C568" s="6" t="s">
-        <v>39</v>
+        <v>151</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -9497,7 +9494,7 @@
         <v>9624</v>
       </c>
       <c r="B569" s="50" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C569" s="6" t="s">
         <v>39</v>
@@ -9508,7 +9505,7 @@
         <v>5875</v>
       </c>
       <c r="B570" s="50" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C570" s="6" t="s">
         <v>39</v>
@@ -9519,7 +9516,7 @@
         <v>7550</v>
       </c>
       <c r="B571" s="50" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C571" s="6" t="s">
         <v>39</v>
@@ -9530,7 +9527,7 @@
         <v>9105</v>
       </c>
       <c r="B572" s="50" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C572" s="6" t="s">
         <v>39</v>
@@ -9541,7 +9538,7 @@
         <v>7773</v>
       </c>
       <c r="B573" s="50" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C573" s="6" t="s">
         <v>39</v>
@@ -9552,7 +9549,7 @@
         <v>8588</v>
       </c>
       <c r="B574" s="50" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C574" s="6" t="s">
         <v>39</v>
@@ -9563,7 +9560,7 @@
         <v>9015</v>
       </c>
       <c r="B575" s="50" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C575" s="6" t="s">
         <v>39</v>
@@ -9574,7 +9571,7 @@
         <v>7646</v>
       </c>
       <c r="B576" s="50" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C576" s="6" t="s">
         <v>39</v>
@@ -9607,7 +9604,7 @@
         <v>9193</v>
       </c>
       <c r="B579" s="50" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C579" s="6" t="s">
         <v>39</v>
@@ -9618,7 +9615,7 @@
         <v>7975</v>
       </c>
       <c r="B580" s="50" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C580" s="6" t="s">
         <v>39</v>
@@ -9640,7 +9637,7 @@
         <v>5541</v>
       </c>
       <c r="B582" s="50" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C582" s="6" t="s">
         <v>40</v>
@@ -9651,7 +9648,7 @@
         <v>7183</v>
       </c>
       <c r="B583" s="50" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C583" s="6" t="s">
         <v>40</v>
@@ -9662,7 +9659,7 @@
         <v>5265</v>
       </c>
       <c r="B584" s="50" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C584" s="6" t="s">
         <v>40</v>
@@ -9673,7 +9670,7 @@
         <v>5640</v>
       </c>
       <c r="B585" s="50" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C585" s="6" t="s">
         <v>40</v>
@@ -9684,7 +9681,7 @@
         <v>6672</v>
       </c>
       <c r="B586" s="50" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C586" s="6" t="s">
         <v>40</v>
@@ -9695,7 +9692,7 @@
         <v>5607</v>
       </c>
       <c r="B587" s="50" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C587" s="6" t="s">
         <v>40</v>
@@ -9717,7 +9714,7 @@
         <v>7174</v>
       </c>
       <c r="B589" s="50" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C589" s="6" t="s">
         <v>40</v>
@@ -9728,7 +9725,7 @@
         <v>8001</v>
       </c>
       <c r="B590" s="50" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C590" s="6" t="s">
         <v>40</v>
@@ -9739,7 +9736,7 @@
         <v>7779</v>
       </c>
       <c r="B591" s="50" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C591" s="6" t="s">
         <v>40</v>
@@ -9750,7 +9747,7 @@
         <v>7626</v>
       </c>
       <c r="B592" s="50" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C592" s="6" t="s">
         <v>40</v>
@@ -9761,7 +9758,7 @@
         <v>5526</v>
       </c>
       <c r="B593" s="50" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C593" s="6" t="s">
         <v>41</v>
@@ -9772,7 +9769,7 @@
         <v>7577</v>
       </c>
       <c r="B594" s="50" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C594" s="6" t="s">
         <v>41</v>
@@ -9783,7 +9780,7 @@
         <v>6435</v>
       </c>
       <c r="B595" s="50" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C595" s="6" t="s">
         <v>41</v>
@@ -9805,7 +9802,7 @@
         <v>5386</v>
       </c>
       <c r="B597" s="50" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C597" s="6" t="s">
         <v>41</v>
@@ -9816,7 +9813,7 @@
         <v>7810</v>
       </c>
       <c r="B598" s="50" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C598" s="6" t="s">
         <v>41</v>
@@ -9827,7 +9824,7 @@
         <v>5785</v>
       </c>
       <c r="B599" s="50" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C599" s="6" t="s">
         <v>38</v>
@@ -9838,7 +9835,7 @@
         <v>8502</v>
       </c>
       <c r="B600" s="50" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C600" s="6" t="s">
         <v>38</v>
@@ -9849,7 +9846,7 @@
         <v>4941</v>
       </c>
       <c r="B601" s="50" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C601" s="6" t="s">
         <v>38</v>
@@ -9860,7 +9857,7 @@
         <v>5674</v>
       </c>
       <c r="B602" s="50" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C602" s="6" t="s">
         <v>38</v>
@@ -9871,7 +9868,7 @@
         <v>8552</v>
       </c>
       <c r="B603" s="50" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C603" s="6" t="s">
         <v>38</v>
@@ -9882,7 +9879,7 @@
         <v>9450</v>
       </c>
       <c r="B604" s="51" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C604" s="6" t="s">
         <v>149</v>
@@ -9904,7 +9901,7 @@
         <v>9106</v>
       </c>
       <c r="B606" s="51" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C606" s="6" t="s">
         <v>149</v>
@@ -9915,7 +9912,7 @@
         <v>8068</v>
       </c>
       <c r="B607" s="51" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C607" s="6" t="s">
         <v>149</v>
@@ -9926,7 +9923,7 @@
         <v>7518</v>
       </c>
       <c r="B608" s="51" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C608" s="6" t="s">
         <v>150</v>
@@ -9937,7 +9934,7 @@
         <v>8658</v>
       </c>
       <c r="B609" s="51" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C609" s="6" t="s">
         <v>151</v>
@@ -9948,7 +9945,7 @@
         <v>6153</v>
       </c>
       <c r="B610" s="51" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C610" s="6" t="s">
         <v>151</v>
@@ -9959,7 +9956,7 @@
         <v>7527</v>
       </c>
       <c r="B611" s="51" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C611" s="6" t="s">
         <v>151</v>
@@ -9970,7 +9967,7 @@
         <v>8917</v>
       </c>
       <c r="B612" s="51" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C612" s="6" t="s">
         <v>151</v>
@@ -9981,7 +9978,7 @@
         <v>6276</v>
       </c>
       <c r="B613" s="51" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C613" s="6" t="s">
         <v>151</v>
@@ -10014,7 +10011,7 @@
         <v>7637</v>
       </c>
       <c r="B616" s="51" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C616" s="6" t="s">
         <v>39</v>
@@ -10025,7 +10022,7 @@
         <v>7791</v>
       </c>
       <c r="B617" s="51" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C617" s="6" t="s">
         <v>39</v>
@@ -10036,7 +10033,7 @@
         <v>5284</v>
       </c>
       <c r="B618" s="51" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C618" s="6" t="s">
         <v>41</v>
@@ -10047,7 +10044,7 @@
         <v>9606</v>
       </c>
       <c r="B619" s="51" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C619" s="6" t="s">
         <v>41</v>
@@ -10058,7 +10055,7 @@
         <v>5330</v>
       </c>
       <c r="B620" s="51" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C620" s="6" t="s">
         <v>41</v>
@@ -10069,7 +10066,7 @@
         <v>7912</v>
       </c>
       <c r="B621" s="51" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C621" s="6" t="s">
         <v>41</v>
@@ -10080,7 +10077,7 @@
         <v>5296</v>
       </c>
       <c r="B622" s="51" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C622" s="6" t="s">
         <v>41</v>
@@ -10102,7 +10099,7 @@
         <v>6834</v>
       </c>
       <c r="B624" s="57" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C624" s="56" t="s">
         <v>149</v>
@@ -10113,7 +10110,7 @@
         <v>9537</v>
       </c>
       <c r="B625" s="57" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C625" s="56" t="s">
         <v>149</v>
@@ -10124,7 +10121,7 @@
         <v>6676</v>
       </c>
       <c r="B626" s="57" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C626" s="56" t="s">
         <v>149</v>
@@ -10135,7 +10132,7 @@
         <v>6342</v>
       </c>
       <c r="B627" s="57" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C627" s="56" t="s">
         <v>150</v>
@@ -10157,7 +10154,7 @@
         <v>7331</v>
       </c>
       <c r="B629" s="57" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C629" s="56" t="s">
         <v>151</v>
@@ -10168,7 +10165,7 @@
         <v>9032</v>
       </c>
       <c r="B630" s="57" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C630" s="56" t="s">
         <v>151</v>
@@ -10179,7 +10176,7 @@
         <v>6140</v>
       </c>
       <c r="B631" s="57" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C631" s="56" t="s">
         <v>151</v>
@@ -10201,7 +10198,7 @@
         <v>8314</v>
       </c>
       <c r="B633" s="57" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C633" s="56" t="s">
         <v>39</v>
@@ -10212,7 +10209,7 @@
         <v>8216</v>
       </c>
       <c r="B634" s="57" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C634" s="56" t="s">
         <v>39</v>
@@ -10223,7 +10220,7 @@
         <v>6820</v>
       </c>
       <c r="B635" s="57" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C635" s="56" t="s">
         <v>39</v>
@@ -10234,7 +10231,7 @@
         <v>5950</v>
       </c>
       <c r="B636" s="57" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C636" s="56" t="s">
         <v>39</v>
@@ -10245,7 +10242,7 @@
         <v>5297</v>
       </c>
       <c r="B637" s="57" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C637" s="56" t="s">
         <v>41</v>
@@ -10256,7 +10253,7 @@
         <v>8265</v>
       </c>
       <c r="B638" s="58" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C638" s="59" t="s">
         <v>149</v>
@@ -10267,7 +10264,7 @@
         <v>7236</v>
       </c>
       <c r="B639" s="58" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C639" s="59" t="s">
         <v>149</v>
@@ -10278,7 +10275,7 @@
         <v>6261</v>
       </c>
       <c r="B640" s="58" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C640" s="59" t="s">
         <v>150</v>
@@ -10289,7 +10286,7 @@
         <v>6433</v>
       </c>
       <c r="B641" s="58" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C641" s="59" t="s">
         <v>151</v>
@@ -10322,7 +10319,7 @@
         <v>7557</v>
       </c>
       <c r="B644" s="58" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C644" s="59" t="s">
         <v>39</v>
@@ -10333,7 +10330,7 @@
         <v>8327</v>
       </c>
       <c r="B645" s="58" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C645" s="59" t="s">
         <v>39</v>
@@ -10344,7 +10341,7 @@
         <v>7188</v>
       </c>
       <c r="B646" s="58" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C646" s="59" t="s">
         <v>39</v>
@@ -10355,7 +10352,7 @@
         <v>8805</v>
       </c>
       <c r="B647" s="58" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C647" s="59" t="s">
         <v>39</v>
@@ -10366,7 +10363,7 @@
         <v>6583</v>
       </c>
       <c r="B648" s="58" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C648" s="59" t="s">
         <v>39</v>
@@ -10388,7 +10385,7 @@
         <v>5606</v>
       </c>
       <c r="B650" s="58" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C650" s="59" t="s">
         <v>40</v>
@@ -10410,7 +10407,7 @@
         <v>5534</v>
       </c>
       <c r="B652" s="58" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C652" s="59" t="s">
         <v>40</v>
@@ -10421,7 +10418,7 @@
         <v>4595</v>
       </c>
       <c r="B653" s="60" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C653" s="59" t="s">
         <v>41</v>
@@ -10443,7 +10440,7 @@
         <v>6429</v>
       </c>
       <c r="B655" s="61" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C655" s="6" t="s">
         <v>149</v>
@@ -10454,7 +10451,7 @@
         <v>7315</v>
       </c>
       <c r="B656" s="61" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C656" s="6" t="s">
         <v>149</v>
@@ -10465,7 +10462,7 @@
         <v>9517</v>
       </c>
       <c r="B657" s="61" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C657" s="6" t="s">
         <v>149</v>
@@ -10476,7 +10473,7 @@
         <v>7191</v>
       </c>
       <c r="B658" s="61" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C658" s="6" t="s">
         <v>149</v>
@@ -10487,7 +10484,7 @@
         <v>6421</v>
       </c>
       <c r="B659" s="61" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C659" s="6" t="s">
         <v>150</v>
@@ -10498,7 +10495,7 @@
         <v>8888</v>
       </c>
       <c r="B660" s="61" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C660" s="6" t="s">
         <v>150</v>
@@ -10509,7 +10506,7 @@
         <v>8666</v>
       </c>
       <c r="B661" s="61" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C661" s="6" t="s">
         <v>151</v>
@@ -10520,7 +10517,7 @@
         <v>6171</v>
       </c>
       <c r="B662" s="61" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C662" s="6" t="s">
         <v>151</v>
@@ -10531,7 +10528,7 @@
         <v>7434</v>
       </c>
       <c r="B663" s="61" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C663" s="6" t="s">
         <v>151</v>
@@ -10542,7 +10539,7 @@
         <v>9660</v>
       </c>
       <c r="B664" s="65" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C664" s="66" t="s">
         <v>41</v>
@@ -10553,7 +10550,7 @@
         <v>7597</v>
       </c>
       <c r="B665" s="67" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C665" s="68" t="s">
         <v>40</v>
@@ -10564,7 +10561,7 @@
         <v>8502</v>
       </c>
       <c r="B666" s="67" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C666" s="68" t="s">
         <v>38</v>
@@ -10575,7 +10572,7 @@
         <v>6726</v>
       </c>
       <c r="B667" s="67" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C667" s="68" t="s">
         <v>38</v>
@@ -10586,7 +10583,7 @@
         <v>8807</v>
       </c>
       <c r="B668" s="56" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C668" s="6" t="s">
         <v>146</v>
@@ -10597,7 +10594,7 @@
         <v>8830</v>
       </c>
       <c r="B669" s="56" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C669" s="6" t="s">
         <v>146</v>
@@ -10608,7 +10605,7 @@
         <v>8467</v>
       </c>
       <c r="B670" s="56" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C670" s="6" t="s">
         <v>146</v>
@@ -10619,7 +10616,7 @@
         <v>9482</v>
       </c>
       <c r="B671" s="56" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C671" s="6" t="s">
         <v>146</v>
@@ -10630,7 +10627,7 @@
         <v>8908</v>
       </c>
       <c r="B672" s="56" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C672" s="6" t="s">
         <v>146</v>
@@ -10641,7 +10638,7 @@
         <v>7231</v>
       </c>
       <c r="B673" s="56" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C673" s="6" t="s">
         <v>147</v>
@@ -10652,7 +10649,7 @@
         <v>8224</v>
       </c>
       <c r="B674" s="56" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C674" s="6" t="s">
         <v>147</v>
@@ -10663,7 +10660,7 @@
         <v>8204</v>
       </c>
       <c r="B675" s="56" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C675" s="6" t="s">
         <v>147</v>
@@ -10674,7 +10671,7 @@
         <v>8131</v>
       </c>
       <c r="B676" s="56" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C676" s="6" t="s">
         <v>149</v>
@@ -10685,7 +10682,7 @@
         <v>8855</v>
       </c>
       <c r="B677" s="56" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C677" s="6" t="s">
         <v>149</v>
@@ -10696,7 +10693,7 @@
         <v>9439</v>
       </c>
       <c r="B678" s="56" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C678" s="6" t="s">
         <v>149</v>
@@ -10707,7 +10704,7 @@
         <v>6601</v>
       </c>
       <c r="B679" s="56" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C679" s="6" t="s">
         <v>149</v>
@@ -10718,7 +10715,7 @@
         <v>7965</v>
       </c>
       <c r="B680" s="56" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C680" s="6" t="s">
         <v>149</v>
@@ -10729,7 +10726,7 @@
         <v>7716</v>
       </c>
       <c r="B681" s="56" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C681" s="6" t="s">
         <v>149</v>
@@ -10740,7 +10737,7 @@
         <v>9413</v>
       </c>
       <c r="B682" s="56" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C682" s="6" t="s">
         <v>149</v>
@@ -10751,7 +10748,7 @@
         <v>6395</v>
       </c>
       <c r="B683" s="56" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C683" s="6" t="s">
         <v>149</v>
@@ -10762,7 +10759,7 @@
         <v>6542</v>
       </c>
       <c r="B684" s="56" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C684" s="6" t="s">
         <v>149</v>
@@ -10773,7 +10770,7 @@
         <v>9151</v>
       </c>
       <c r="B685" s="56" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C685" s="6" t="s">
         <v>149</v>
@@ -10784,7 +10781,7 @@
         <v>6479</v>
       </c>
       <c r="B686" s="56" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C686" s="6" t="s">
         <v>149</v>
@@ -10806,7 +10803,7 @@
         <v>6510</v>
       </c>
       <c r="B688" s="56" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C688" s="6" t="s">
         <v>149</v>
@@ -10817,7 +10814,7 @@
         <v>6420</v>
       </c>
       <c r="B689" s="56" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C689" s="6" t="s">
         <v>149</v>
@@ -10828,7 +10825,7 @@
         <v>6442</v>
       </c>
       <c r="B690" s="56" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C690" s="6" t="s">
         <v>149</v>
@@ -10839,7 +10836,7 @@
         <v>6423</v>
       </c>
       <c r="B691" s="56" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C691" s="6" t="s">
         <v>149</v>
@@ -10850,7 +10847,7 @@
         <v>9477</v>
       </c>
       <c r="B692" s="56" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C692" s="6" t="s">
         <v>149</v>
@@ -10861,7 +10858,7 @@
         <v>7442</v>
       </c>
       <c r="B693" s="56" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C693" s="6" t="s">
         <v>149</v>
@@ -10872,7 +10869,7 @@
         <v>8443</v>
       </c>
       <c r="B694" s="56" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C694" s="6" t="s">
         <v>149</v>
@@ -10883,7 +10880,7 @@
         <v>7193</v>
       </c>
       <c r="B695" s="56" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C695" s="6" t="s">
         <v>149</v>
@@ -10894,7 +10891,7 @@
         <v>6749</v>
       </c>
       <c r="B696" s="56" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C696" s="6" t="s">
         <v>149</v>
@@ -10905,7 +10902,7 @@
         <v>6406</v>
       </c>
       <c r="B697" s="56" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C697" s="6" t="s">
         <v>149</v>
@@ -10916,7 +10913,7 @@
         <v>6379</v>
       </c>
       <c r="B698" s="56" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C698" s="6" t="s">
         <v>149</v>
@@ -10927,7 +10924,7 @@
         <v>8274</v>
       </c>
       <c r="B699" s="56" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C699" s="6" t="s">
         <v>149</v>
@@ -10938,7 +10935,7 @@
         <v>7532</v>
       </c>
       <c r="B700" s="56" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C700" s="6" t="s">
         <v>149</v>
@@ -10949,7 +10946,7 @@
         <v>8047</v>
       </c>
       <c r="B701" s="56" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C701" s="6" t="s">
         <v>149</v>
@@ -10960,7 +10957,7 @@
         <v>7700</v>
       </c>
       <c r="B702" s="56" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C702" s="6" t="s">
         <v>149</v>
@@ -10971,7 +10968,7 @@
         <v>9449</v>
       </c>
       <c r="B703" s="56" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C703" s="6" t="s">
         <v>149</v>
@@ -10982,7 +10979,7 @@
         <v>6170</v>
       </c>
       <c r="B704" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C704" s="6" t="s">
         <v>150</v>
@@ -10993,7 +10990,7 @@
         <v>6174</v>
       </c>
       <c r="B705" s="56" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C705" s="6" t="s">
         <v>150</v>
@@ -11004,7 +11001,7 @@
         <v>9581</v>
       </c>
       <c r="B706" s="56" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C706" s="6" t="s">
         <v>150</v>
@@ -11026,7 +11023,7 @@
         <v>6875</v>
       </c>
       <c r="B708" s="56" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C708" s="6" t="s">
         <v>150</v>
@@ -11037,7 +11034,7 @@
         <v>6463</v>
       </c>
       <c r="B709" s="56" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C709" s="6" t="s">
         <v>150</v>
@@ -11070,7 +11067,7 @@
         <v>6343</v>
       </c>
       <c r="B712" s="56" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C712" s="6" t="s">
         <v>151</v>
@@ -11103,7 +11100,7 @@
         <v>5899</v>
       </c>
       <c r="B715" s="56" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C715" s="6" t="s">
         <v>39</v>
@@ -11125,7 +11122,7 @@
         <v>6921</v>
       </c>
       <c r="B717" s="56" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C717" s="6" t="s">
         <v>39</v>
@@ -11136,7 +11133,7 @@
         <v>8638</v>
       </c>
       <c r="B718" s="56" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C718" s="6" t="s">
         <v>39</v>
@@ -11202,7 +11199,7 @@
         <v>5850</v>
       </c>
       <c r="B724" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C724" s="6" t="s">
         <v>39</v>
@@ -11213,7 +11210,7 @@
         <v>6484</v>
       </c>
       <c r="B725" s="56" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C725" s="6" t="s">
         <v>39</v>
@@ -11235,7 +11232,7 @@
         <v>5841</v>
       </c>
       <c r="B727" s="56" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C727" s="6" t="s">
         <v>39</v>
@@ -11246,7 +11243,7 @@
         <v>7962</v>
       </c>
       <c r="B728" s="56" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C728" s="6" t="s">
         <v>39</v>
@@ -11257,7 +11254,7 @@
         <v>8918</v>
       </c>
       <c r="B729" s="56" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C729" s="6" t="s">
         <v>39</v>
@@ -11268,7 +11265,7 @@
         <v>6572</v>
       </c>
       <c r="B730" s="56" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C730" s="6" t="s">
         <v>39</v>
@@ -11279,7 +11276,7 @@
         <v>5857</v>
       </c>
       <c r="B731" s="56" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C731" s="6" t="s">
         <v>39</v>
@@ -11301,7 +11298,7 @@
         <v>6789</v>
       </c>
       <c r="B733" s="56" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C733" s="6" t="s">
         <v>39</v>
@@ -11334,7 +11331,7 @@
         <v>8824</v>
       </c>
       <c r="B736" s="56" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C736" s="6" t="s">
         <v>39</v>
@@ -11345,7 +11342,7 @@
         <v>5898</v>
       </c>
       <c r="B737" s="56" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C737" s="6" t="s">
         <v>39</v>
@@ -11356,7 +11353,7 @@
         <v>8826</v>
       </c>
       <c r="B738" s="56" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C738" s="6" t="s">
         <v>39</v>
@@ -11367,7 +11364,7 @@
         <v>8478</v>
       </c>
       <c r="B739" s="56" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C739" s="6" t="s">
         <v>39</v>
@@ -11378,7 +11375,7 @@
         <v>5937</v>
       </c>
       <c r="B740" s="56" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C740" s="6" t="s">
         <v>39</v>
@@ -11389,7 +11386,7 @@
         <v>5916</v>
       </c>
       <c r="B741" s="56" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C741" s="6" t="s">
         <v>39</v>
@@ -11411,7 +11408,7 @@
         <v>5882</v>
       </c>
       <c r="B743" s="56" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C743" s="6" t="s">
         <v>39</v>
@@ -11422,7 +11419,7 @@
         <v>5958</v>
       </c>
       <c r="B744" s="56" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C744" s="6" t="s">
         <v>39</v>
@@ -11433,7 +11430,7 @@
         <v>9244</v>
       </c>
       <c r="B745" s="56" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C745" s="6" t="s">
         <v>39</v>
@@ -11444,7 +11441,7 @@
         <v>6662</v>
       </c>
       <c r="B746" s="56" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C746" s="6" t="s">
         <v>39</v>
@@ -11455,7 +11452,7 @@
         <v>8369</v>
       </c>
       <c r="B747" s="56" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C747" s="6" t="s">
         <v>39</v>
@@ -11477,7 +11474,7 @@
         <v>6009</v>
       </c>
       <c r="B749" s="71" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C749" s="72" t="s">
         <v>39</v>
@@ -11488,7 +11485,7 @@
         <v>5845</v>
       </c>
       <c r="B750" s="71" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C750" s="72" t="s">
         <v>39</v>
@@ -11499,7 +11496,7 @@
         <v>5840</v>
       </c>
       <c r="B751" s="71" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C751" s="72" t="s">
         <v>39</v>
@@ -11510,7 +11507,7 @@
         <v>5989</v>
       </c>
       <c r="B752" s="71" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C752" s="72" t="s">
         <v>39</v>
@@ -11521,7 +11518,7 @@
         <v>5528</v>
       </c>
       <c r="B753" s="73" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C753" s="73" t="s">
         <v>41</v>
@@ -11532,7 +11529,7 @@
         <v>7580</v>
       </c>
       <c r="B754" s="74" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C754" s="74" t="s">
         <v>41</v>
@@ -11543,7 +11540,7 @@
         <v>4867</v>
       </c>
       <c r="B755" s="75" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C755" s="75" t="s">
         <v>38</v>
@@ -11554,7 +11551,7 @@
         <v>7767</v>
       </c>
       <c r="B756" s="75" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C756" s="75" t="s">
         <v>38</v>
@@ -11576,7 +11573,7 @@
         <v>6187</v>
       </c>
       <c r="B758" s="76" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C758" s="6" t="s">
         <v>150</v>
@@ -11587,7 +11584,7 @@
         <v>6249</v>
       </c>
       <c r="B759" s="77" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C759" s="6" t="s">
         <v>150</v>
@@ -11598,7 +11595,7 @@
         <v>6180</v>
       </c>
       <c r="B760" s="77" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C760" s="6" t="s">
         <v>150</v>
@@ -11609,7 +11606,7 @@
         <v>6242</v>
       </c>
       <c r="B761" s="78" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C761" s="6" t="s">
         <v>150</v>
@@ -11620,7 +11617,7 @@
         <v>6788</v>
       </c>
       <c r="B762" s="78" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C762" s="6" t="s">
         <v>150</v>
@@ -11631,7 +11628,7 @@
         <v>8254</v>
       </c>
       <c r="B763" s="78" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C763" s="6" t="s">
         <v>150</v>
@@ -11642,7 +11639,7 @@
         <v>8468</v>
       </c>
       <c r="B764" s="78" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C764" s="6" t="s">
         <v>150</v>
@@ -11653,7 +11650,7 @@
         <v>8624</v>
       </c>
       <c r="B765" s="78" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C765" s="6" t="s">
         <v>150</v>
@@ -11664,7 +11661,7 @@
         <v>7298</v>
       </c>
       <c r="B766" s="78" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C766" s="6" t="s">
         <v>150</v>
@@ -11675,7 +11672,7 @@
         <v>6333</v>
       </c>
       <c r="B767" s="78" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C767" s="6" t="s">
         <v>150</v>
@@ -11686,7 +11683,7 @@
         <v>8713</v>
       </c>
       <c r="B768" s="78" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C768" s="6" t="s">
         <v>150</v>
@@ -11697,7 +11694,7 @@
         <v>8600</v>
       </c>
       <c r="B769" s="78" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C769" s="6" t="s">
         <v>150</v>
@@ -11708,7 +11705,7 @@
         <v>9209</v>
       </c>
       <c r="B770" s="80" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C770" s="66" t="s">
         <v>150</v>
@@ -11719,7 +11716,7 @@
         <v>6160</v>
       </c>
       <c r="B771" s="81" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C771" s="56" t="s">
         <v>150</v>
@@ -11730,7 +11727,7 @@
         <v>6968</v>
       </c>
       <c r="B772" s="81" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C772" s="56" t="s">
         <v>150</v>
@@ -11741,7 +11738,7 @@
         <v>8574</v>
       </c>
       <c r="B773" s="81" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C773" s="56" t="s">
         <v>150</v>
@@ -11752,7 +11749,7 @@
         <v>6892</v>
       </c>
       <c r="B774" s="81" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C774" s="56" t="s">
         <v>150</v>
@@ -11763,7 +11760,7 @@
         <v>8276</v>
       </c>
       <c r="B775" s="81" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C775" s="56" t="s">
         <v>150</v>
@@ -11774,7 +11771,7 @@
         <v>9029</v>
       </c>
       <c r="B776" s="81" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C776" s="56" t="s">
         <v>150</v>
@@ -11785,7 +11782,7 @@
         <v>9179</v>
       </c>
       <c r="B777" s="82" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C777" s="83" t="s">
         <v>150</v>
